--- a/data/LSR3_H_2024-01-22.xlsx
+++ b/data/LSR3_H_2024-01-22.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4DC28F-7A56-AB48-87B9-A39D92320524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF850F3-35FC-C94E-970A-B4DD60DA6D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24460" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21080" yWindow="-17900" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="257">
   <si>
     <t>arm_name</t>
   </si>
@@ -767,13 +767,49 @@
   </si>
   <si>
     <t>anticholinergic_symptom_n</t>
+  </si>
+  <si>
+    <t>study_year</t>
+  </si>
+  <si>
+    <t>study_doi</t>
+  </si>
+  <si>
+    <t>10.1212/CPJ.0000000000200175</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1056/nejmoa1911772</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41537-023-00385-6</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1111/cts.13512</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41398-021-01331-9</t>
+  </si>
+  <si>
+    <t>https://dx.doi.org/10.1016/j.sleep.2023.04.019</t>
+  </si>
+  <si>
+    <t>duration_unit</t>
+  </si>
+  <si>
+    <t>weeks</t>
+  </si>
+  <si>
+    <t>overall_baseline_n</t>
+  </si>
+  <si>
+    <t>depression_baseline_n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,8 +825,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,6 +877,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -843,10 +893,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -861,8 +912,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1165,481 +1222,497 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DY26"/>
+  <dimension ref="A1:ED26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="34" max="34" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
+    <col min="15" max="16" width="9" customWidth="1"/>
+    <col min="37" max="38" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:129" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:134" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AL1" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BZ1" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="7" t="s">
+      <c r="CZ1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="CV1" s="7" t="s">
+      <c r="DA1" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DY1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DZ1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="EA1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="EB1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="DX1" s="1" t="s">
+      <c r="EC1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="DY1" s="1" t="s">
+      <c r="ED1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>144</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>145</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>146</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>147</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>148</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>149</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>150</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>6</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q2" t="s">
         <v>151</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>152</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>153</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>142</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>154</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>142</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>129</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Z2" t="s">
         <v>142</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AA2" t="s">
         <v>155</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>142</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>157</v>
       </c>
       <c r="AC2" t="s">
         <v>156</v>
@@ -1651,199 +1724,210 @@
         <v>157</v>
       </c>
       <c r="AF2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI2" t="s">
         <v>159</v>
       </c>
-      <c r="AG2">
+      <c r="AJ2">
         <v>23</v>
       </c>
-      <c r="AI2">
+      <c r="AL2" s="11"/>
+      <c r="AM2">
         <v>-11.5</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>20.12</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AO2" t="s">
         <v>131</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AP2" t="s">
         <v>132</v>
       </c>
-      <c r="AM2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN2" t="s">
+      <c r="AQ2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR2" t="s">
         <v>160</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>24</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>13.1</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>-2.5</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>7.94</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AW2" t="s">
         <v>131</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AX2" t="s">
         <v>132</v>
       </c>
-      <c r="AU2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BL2" t="s">
+      <c r="AY2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BP2" t="s">
         <v>161</v>
       </c>
-      <c r="BM2">
+      <c r="BQ2">
         <v>23</v>
       </c>
-      <c r="BN2">
+      <c r="BR2">
         <v>-25.1</v>
       </c>
-      <c r="BO2">
+      <c r="BS2">
         <v>0.8</v>
       </c>
-      <c r="BP2">
+      <c r="BT2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BU2" t="s">
         <v>131</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BV2" t="s">
         <v>132</v>
       </c>
-      <c r="BS2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS2">
+      <c r="BW2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ2" s="11"/>
+      <c r="CX2">
         <v>18</v>
       </c>
-      <c r="CT2">
+      <c r="CY2">
         <v>25</v>
       </c>
-      <c r="CW2" s="9"/>
-      <c r="CX2" s="9"/>
-      <c r="CY2">
+      <c r="DB2" s="9"/>
+      <c r="DC2" s="9"/>
+      <c r="DD2">
         <v>4</v>
       </c>
-      <c r="CZ2">
+      <c r="DE2">
         <v>25</v>
       </c>
-      <c r="DC2">
+      <c r="DH2">
         <v>3</v>
       </c>
-      <c r="DD2">
+      <c r="DI2">
         <v>25</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>2</v>
       </c>
-      <c r="DF2">
+      <c r="DK2">
         <v>25</v>
       </c>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="9"/>
-      <c r="DM2">
+      <c r="DP2" s="9"/>
+      <c r="DQ2" s="9"/>
+      <c r="DR2">
         <v>13</v>
       </c>
-      <c r="DN2">
+      <c r="DS2">
         <v>25</v>
       </c>
-      <c r="DO2" s="8">
+      <c r="DT2" s="8">
         <v>2</v>
       </c>
-      <c r="DW2" t="s">
+      <c r="EB2" t="s">
         <v>139</v>
       </c>
-      <c r="DX2" t="s">
+      <c r="EC2" t="s">
         <v>162</v>
       </c>
-      <c r="DY2" t="s">
+      <c r="ED2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>163</v>
       </c>
       <c r="B3" t="s">
         <v>144</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>145</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>163</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>129</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>147</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>148</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>149</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>150</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>6</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q3" t="s">
         <v>164</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>143</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>164</v>
       </c>
-      <c r="S3" t="s">
+      <c r="V3" t="s">
         <v>165</v>
       </c>
-      <c r="T3" t="s">
+      <c r="W3" t="s">
         <v>166</v>
       </c>
-      <c r="U3" t="s">
+      <c r="X3" t="s">
         <v>165</v>
       </c>
-      <c r="V3" t="s">
+      <c r="Y3" t="s">
         <v>129</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Z3" t="s">
         <v>165</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AA3" t="s">
         <v>129</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
         <v>165</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>157</v>
       </c>
       <c r="AC3" t="s">
         <v>156</v>
@@ -1855,3338 +1939,3628 @@
         <v>157</v>
       </c>
       <c r="AF3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI3" t="s">
         <v>159</v>
       </c>
-      <c r="AG3">
+      <c r="AJ3">
         <v>14</v>
       </c>
-      <c r="AI3">
+      <c r="AL3" s="11"/>
+      <c r="AM3">
         <v>-17.3</v>
       </c>
-      <c r="AJ3">
+      <c r="AN3">
         <v>19.57</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AO3" t="s">
         <v>131</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AP3" t="s">
         <v>132</v>
       </c>
-      <c r="AM3" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN3" t="s">
+      <c r="AQ3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR3" t="s">
         <v>160</v>
       </c>
-      <c r="AO3">
+      <c r="AS3">
         <v>14</v>
       </c>
-      <c r="AP3">
+      <c r="AT3">
         <v>14.7</v>
       </c>
-      <c r="AQ3">
+      <c r="AU3">
         <v>-1.4</v>
       </c>
-      <c r="AR3">
+      <c r="AV3">
         <v>7.71</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AW3" t="s">
         <v>131</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AX3" t="s">
         <v>132</v>
       </c>
-      <c r="AU3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BL3" t="s">
+      <c r="AY3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BP3" t="s">
         <v>161</v>
       </c>
-      <c r="BM3">
+      <c r="BQ3">
         <v>14</v>
       </c>
-      <c r="BN3">
+      <c r="BR3">
         <v>-24.7</v>
       </c>
-      <c r="BO3">
+      <c r="BS3">
         <v>-0.3</v>
       </c>
-      <c r="BP3">
+      <c r="BT3">
         <v>1.99</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BU3" t="s">
         <v>131</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BV3" t="s">
         <v>132</v>
       </c>
-      <c r="BS3" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS3">
+      <c r="BW3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ3" s="11"/>
+      <c r="CX3">
         <v>12</v>
       </c>
-      <c r="CT3">
+      <c r="CY3">
         <v>14</v>
       </c>
-      <c r="CW3">
+      <c r="DB3">
         <v>0</v>
       </c>
-      <c r="CX3">
+      <c r="DC3">
         <v>14</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>1</v>
       </c>
-      <c r="CZ3">
+      <c r="DE3">
         <v>14</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>1</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>14</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>2</v>
       </c>
-      <c r="DF3">
+      <c r="DK3">
         <v>14</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>1</v>
       </c>
-      <c r="DL3">
+      <c r="DQ3">
         <v>14</v>
       </c>
-      <c r="DM3">
+      <c r="DR3">
         <v>11</v>
       </c>
-      <c r="DN3">
+      <c r="DS3">
         <v>14</v>
       </c>
-      <c r="DO3">
+      <c r="DT3">
         <v>1</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>14</v>
       </c>
-      <c r="DW3" t="s">
+      <c r="EB3" t="s">
         <v>163</v>
       </c>
-      <c r="DX3" t="s">
+      <c r="EC3" t="s">
         <v>162</v>
       </c>
-      <c r="DY3" t="s">
+      <c r="ED3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>167</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="11">
+        <v>2020</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>145</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>127</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>168</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>128</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>148</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>169</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>120</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>170</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>43</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q4" t="s">
         <v>140</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>171</v>
       </c>
-      <c r="R4" t="s">
+      <c r="U4" t="s">
         <v>172</v>
       </c>
-      <c r="S4" t="s">
+      <c r="V4" t="s">
         <v>171</v>
       </c>
-      <c r="T4" t="s">
+      <c r="W4" t="s">
         <v>153</v>
       </c>
-      <c r="U4" t="s">
+      <c r="X4" t="s">
         <v>171</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Y4" t="s">
         <v>166</v>
       </c>
-      <c r="W4" t="s">
+      <c r="Z4" t="s">
         <v>171</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AA4" t="s">
         <v>155</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
         <v>171</v>
       </c>
-      <c r="Z4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE4" t="s">
         <v>158</v>
       </c>
-      <c r="AC4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE4" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI4" t="s">
         <v>130</v>
       </c>
-      <c r="AG4">
+      <c r="AJ4">
         <v>120</v>
       </c>
-      <c r="AH4">
+      <c r="AK4">
         <v>101.4</v>
       </c>
-      <c r="AI4">
+      <c r="AL4" s="11">
+        <v>120</v>
+      </c>
+      <c r="AM4">
         <v>-17.2</v>
       </c>
-      <c r="AJ4">
+      <c r="AN4">
         <v>18.63</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AO4" t="s">
         <v>131</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AP4" t="s">
         <v>132</v>
       </c>
-      <c r="AM4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN4" t="s">
+      <c r="AQ4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR4" t="s">
         <v>134</v>
       </c>
-      <c r="AO4">
+      <c r="AS4">
         <v>120</v>
       </c>
-      <c r="AP4">
+      <c r="AT4">
         <v>25.8</v>
       </c>
-      <c r="AQ4">
+      <c r="AU4">
         <v>-5.5</v>
       </c>
-      <c r="AR4">
+      <c r="AV4">
         <v>5.48</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AW4" t="s">
         <v>131</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AX4" t="s">
         <v>132</v>
       </c>
-      <c r="AU4" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV4" t="s">
+      <c r="AY4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>135</v>
       </c>
-      <c r="AW4">
+      <c r="BA4">
         <v>120</v>
       </c>
-      <c r="AX4">
+      <c r="BB4">
         <v>24.7</v>
       </c>
-      <c r="AY4">
+      <c r="BC4">
         <v>-3.1</v>
       </c>
-      <c r="AZ4">
+      <c r="BD4">
         <v>4.38</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BE4" t="s">
         <v>131</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BF4" t="s">
         <v>132</v>
       </c>
-      <c r="BC4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT4" t="s">
+      <c r="BG4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX4" t="s">
         <v>136</v>
       </c>
-      <c r="BU4">
+      <c r="BY4">
         <v>120</v>
       </c>
-      <c r="BV4">
+      <c r="BZ4" s="11">
+        <v>120</v>
+      </c>
+      <c r="CA4">
         <v>13.1</v>
       </c>
-      <c r="BW4">
+      <c r="CB4">
         <v>-3.3</v>
       </c>
-      <c r="BX4">
+      <c r="CC4">
         <v>6.57</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="CD4" t="s">
         <v>131</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CE4" t="s">
         <v>132</v>
       </c>
-      <c r="CA4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CB4" t="s">
+      <c r="CF4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CG4" t="s">
         <v>137</v>
       </c>
-      <c r="CC4">
+      <c r="CH4">
         <v>120</v>
       </c>
-      <c r="CD4">
+      <c r="CI4">
         <v>75.400000000000006</v>
       </c>
-      <c r="CE4">
+      <c r="CJ4">
         <v>0.3</v>
       </c>
-      <c r="CF4">
+      <c r="CK4">
         <v>1.9</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CL4" t="s">
         <v>131</v>
       </c>
-      <c r="CH4" t="s">
+      <c r="CM4" t="s">
         <v>132</v>
       </c>
-      <c r="CI4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ4" t="s">
+      <c r="CN4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CO4" t="s">
         <v>173</v>
       </c>
-      <c r="CK4" t="s">
+      <c r="CP4" t="s">
         <v>138</v>
       </c>
-      <c r="CL4">
+      <c r="CQ4">
         <v>114</v>
       </c>
-      <c r="CN4">
+      <c r="CS4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CO4">
+      <c r="CT4">
         <v>28</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CU4" t="s">
         <v>131</v>
       </c>
-      <c r="CQ4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR4" t="s">
+      <c r="CV4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CW4" t="s">
         <v>132</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>55</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>120</v>
       </c>
-      <c r="CW4">
+      <c r="DB4">
         <v>2</v>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>120</v>
       </c>
-      <c r="DA4">
+      <c r="DF4">
         <v>11</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>120</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>6</v>
       </c>
-      <c r="DD4">
+      <c r="DI4">
         <v>120</v>
       </c>
-      <c r="DE4">
+      <c r="DJ4">
         <v>8</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>120</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>0</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>120</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>6</v>
       </c>
-      <c r="DL4">
+      <c r="DQ4">
         <v>120</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>4</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>120</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>1</v>
       </c>
-      <c r="DR4">
+      <c r="DW4">
         <v>120</v>
       </c>
-      <c r="DS4">
+      <c r="DX4">
         <v>4</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>120</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>1</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>120</v>
       </c>
-      <c r="DW4" t="s">
+      <c r="EB4" t="s">
         <v>139</v>
       </c>
-      <c r="DX4" t="s">
+      <c r="EC4" t="s">
         <v>162</v>
       </c>
-      <c r="DY4" t="s">
+      <c r="ED4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>167</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="11">
+        <v>2020</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>145</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>163</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>129</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>128</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>148</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>169</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>125</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>170</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>46</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q5" t="s">
         <v>174</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="R5" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="R5" t="s">
+      <c r="U5" t="s">
         <v>172</v>
       </c>
-      <c r="S5" t="s">
+      <c r="V5" t="s">
         <v>175</v>
       </c>
-      <c r="T5" t="s">
+      <c r="W5" t="s">
         <v>176</v>
       </c>
-      <c r="U5" t="s">
+      <c r="X5" t="s">
         <v>175</v>
       </c>
-      <c r="V5" t="s">
+      <c r="Y5" t="s">
         <v>129</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Z5" t="s">
         <v>175</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AA5" t="s">
         <v>177</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AB5" t="s">
         <v>175</v>
       </c>
-      <c r="Z5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE5" t="s">
         <v>158</v>
       </c>
-      <c r="AC5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI5" t="s">
         <v>130</v>
       </c>
-      <c r="AG5">
+      <c r="AJ5">
         <v>125</v>
       </c>
-      <c r="AH5">
+      <c r="AK5">
         <v>99.7</v>
       </c>
-      <c r="AI5">
+      <c r="AL5" s="11">
+        <v>125</v>
+      </c>
+      <c r="AM5">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="AJ5">
+      <c r="AN5">
         <v>17.89</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AO5" t="s">
         <v>131</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AP5" t="s">
         <v>132</v>
       </c>
-      <c r="AM5" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN5" t="s">
+      <c r="AQ5" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR5" t="s">
         <v>134</v>
       </c>
-      <c r="AO5">
+      <c r="AS5">
         <v>125</v>
       </c>
-      <c r="AP5">
+      <c r="AT5">
         <v>25.4</v>
       </c>
-      <c r="AQ5">
+      <c r="AU5">
         <v>-3.9</v>
       </c>
-      <c r="AR5">
+      <c r="AV5">
         <v>5.59</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AW5" t="s">
         <v>131</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AX5" t="s">
         <v>132</v>
       </c>
-      <c r="AU5" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV5" t="s">
+      <c r="AY5" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ5" t="s">
         <v>135</v>
       </c>
-      <c r="AW5">
+      <c r="BA5">
         <v>125</v>
       </c>
-      <c r="AX5">
+      <c r="BB5">
         <v>24.9</v>
       </c>
-      <c r="AY5">
+      <c r="BC5">
         <v>-1.6</v>
       </c>
-      <c r="AZ5">
+      <c r="BD5">
         <v>4.47</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BE5" t="s">
         <v>131</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BF5" t="s">
         <v>132</v>
       </c>
-      <c r="BC5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT5" t="s">
+      <c r="BG5" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX5" t="s">
         <v>136</v>
       </c>
-      <c r="BU5">
+      <c r="BY5">
         <v>125</v>
       </c>
-      <c r="BV5">
+      <c r="BZ5" s="11">
+        <v>125</v>
+      </c>
+      <c r="CA5">
         <v>12.6</v>
       </c>
-      <c r="BW5">
+      <c r="CB5">
         <v>-1.6</v>
       </c>
-      <c r="BX5">
+      <c r="CC5">
         <v>6.71</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="CD5" t="s">
         <v>131</v>
       </c>
-      <c r="BZ5" t="s">
+      <c r="CE5" t="s">
         <v>132</v>
       </c>
-      <c r="CA5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CB5" t="s">
+      <c r="CF5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CG5" t="s">
         <v>137</v>
       </c>
-      <c r="CC5">
+      <c r="CH5">
         <v>125</v>
       </c>
-      <c r="CD5">
+      <c r="CI5">
         <v>75.400000000000006</v>
       </c>
-      <c r="CE5">
+      <c r="CJ5">
         <v>-0.1</v>
       </c>
-      <c r="CF5">
+      <c r="CK5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CL5" t="s">
         <v>131</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="CM5" t="s">
         <v>132</v>
       </c>
-      <c r="CI5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ5" t="s">
+      <c r="CN5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CO5" t="s">
         <v>173</v>
       </c>
-      <c r="CK5" t="s">
+      <c r="CP5" t="s">
         <v>138</v>
       </c>
-      <c r="CL5">
+      <c r="CQ5">
         <v>113</v>
       </c>
-      <c r="CN5">
+      <c r="CS5">
         <v>-1.3838053097345131</v>
       </c>
-      <c r="CO5">
+      <c r="CT5">
         <v>28</v>
       </c>
-      <c r="CP5" t="s">
+      <c r="CU5" t="s">
         <v>131</v>
       </c>
-      <c r="CQ5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR5" t="s">
+      <c r="CV5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CW5" t="s">
         <v>132</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>63</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>125</v>
       </c>
-      <c r="CW5">
+      <c r="DB5">
         <v>9</v>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>125</v>
       </c>
-      <c r="DA5">
+      <c r="DF5">
         <v>15</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>125</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>4</v>
       </c>
-      <c r="DD5">
+      <c r="DI5">
         <v>125</v>
       </c>
-      <c r="DE5">
+      <c r="DJ5">
         <v>6</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>125</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>0</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>125</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>6</v>
       </c>
-      <c r="DL5">
+      <c r="DQ5">
         <v>125</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>13</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>125</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>0</v>
       </c>
-      <c r="DR5">
+      <c r="DW5">
         <v>125</v>
       </c>
-      <c r="DS5">
+      <c r="DX5">
         <v>4</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>125</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>1</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>125</v>
       </c>
-      <c r="DW5" t="s">
+      <c r="EB5" t="s">
         <v>163</v>
       </c>
-      <c r="DX5" t="s">
+      <c r="EC5" t="s">
         <v>162</v>
       </c>
-      <c r="DY5" t="s">
+      <c r="ED5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>178</v>
       </c>
       <c r="B6" t="s">
         <v>179</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>145</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>127</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>180</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>128</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>148</v>
       </c>
-      <c r="I6" s="2">
+      <c r="K6" s="2">
         <v>435</v>
       </c>
-      <c r="J6" s="3">
+      <c r="L6" s="3">
         <v>144</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>182</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>6</v>
       </c>
-      <c r="N6" s="2">
+      <c r="P6" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q6" s="2">
         <v>22</v>
       </c>
-      <c r="O6" s="3">
+      <c r="R6" s="3">
         <v>144</v>
       </c>
-      <c r="R6" s="2">
+      <c r="U6" s="2">
         <v>34</v>
       </c>
-      <c r="S6" s="2">
+      <c r="V6" s="2">
         <v>144</v>
       </c>
-      <c r="Z6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC6" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI6" t="s">
         <v>130</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AJ6" s="2">
         <v>142</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AK6" s="2">
         <v>102</v>
       </c>
-      <c r="AI6">
+      <c r="AL6" s="11">
+        <v>142</v>
+      </c>
+      <c r="AM6">
         <v>-16.899999999999999</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AN6" s="2">
         <v>19.07</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AO6" t="s">
         <v>131</v>
       </c>
-      <c r="AL6" t="s">
+      <c r="AP6" t="s">
         <v>132</v>
       </c>
-      <c r="AM6" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW6" t="s">
+      <c r="AQ6" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ6" s="11"/>
+      <c r="EB6" t="s">
         <v>139</v>
       </c>
-      <c r="DX6" t="s">
+      <c r="EC6" t="s">
         <v>162</v>
       </c>
-      <c r="DY6" t="s">
+      <c r="ED6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>183</v>
       </c>
       <c r="B7" t="s">
         <v>179</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>145</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>127</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>184</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>128</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>148</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>435</v>
       </c>
-      <c r="J7" s="3">
+      <c r="L7" s="3">
         <v>145</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>182</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q7" s="2">
         <v>29</v>
       </c>
-      <c r="O7" s="3">
+      <c r="R7" s="3">
         <v>145</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>27</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>145</v>
       </c>
-      <c r="Z7" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC7" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI7" t="s">
         <v>130</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AJ7" s="2">
         <v>145</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AK7" s="2">
         <v>102</v>
       </c>
-      <c r="AI7">
+      <c r="AL7" s="11">
+        <v>145</v>
+      </c>
+      <c r="AM7">
         <v>-19.600000000000001</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>19.27</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AO7" t="s">
         <v>131</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AP7" t="s">
         <v>132</v>
       </c>
-      <c r="AM7" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW7" t="s">
+      <c r="AQ7" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ7" s="11"/>
+      <c r="EB7" t="s">
         <v>139</v>
       </c>
-      <c r="DX7" t="s">
+      <c r="EC7" t="s">
         <v>162</v>
       </c>
-      <c r="DY7" t="s">
+      <c r="ED7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>185</v>
       </c>
       <c r="B8" t="s">
         <v>179</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>145</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>163</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>129</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>128</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>148</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>181</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>146</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>182</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="N8" s="2">
+      <c r="P8" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q8" s="2">
         <v>26</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>146</v>
       </c>
-      <c r="R8" s="2">
+      <c r="U8" s="2">
         <v>27</v>
       </c>
-      <c r="S8" s="2">
+      <c r="V8" s="2">
         <v>146</v>
       </c>
-      <c r="Z8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE8" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI8" t="s">
         <v>130</v>
       </c>
-      <c r="AG8">
+      <c r="AJ8">
         <v>145</v>
       </c>
-      <c r="AH8" s="2">
+      <c r="AK8" s="2">
         <v>102</v>
       </c>
-      <c r="AI8">
+      <c r="AL8" s="11">
+        <v>145</v>
+      </c>
+      <c r="AM8">
         <v>-19.3</v>
       </c>
-      <c r="AJ8" s="2">
+      <c r="AN8" s="2">
         <v>18.059999999999999</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AO8" t="s">
         <v>131</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AP8" t="s">
         <v>132</v>
       </c>
-      <c r="AM8" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW8" t="s">
+      <c r="AQ8" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ8" s="11"/>
+      <c r="EB8" t="s">
         <v>163</v>
       </c>
-      <c r="DX8" t="s">
+      <c r="EC8" t="s">
         <v>162</v>
       </c>
-      <c r="DY8" t="s">
+      <c r="ED8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>186</v>
       </c>
       <c r="B9" t="s">
         <v>187</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>145</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>127</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>184</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>128</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>148</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>188</v>
       </c>
-      <c r="J9" s="2">
+      <c r="L9" s="2">
         <v>155</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>182</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>6</v>
       </c>
-      <c r="N9" s="2">
+      <c r="P9" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q9" s="2">
         <v>23</v>
       </c>
-      <c r="O9" s="2">
+      <c r="R9" s="2">
         <v>155</v>
       </c>
-      <c r="R9" s="2">
+      <c r="U9" s="2">
         <v>34</v>
       </c>
-      <c r="S9" s="2">
+      <c r="V9" s="2">
         <v>155</v>
       </c>
-      <c r="Z9" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AC9" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC9" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF9" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI9" t="s">
         <v>130</v>
       </c>
-      <c r="AG9" s="2">
+      <c r="AJ9" s="2">
         <v>153</v>
       </c>
-      <c r="AH9" s="2">
+      <c r="AK9" s="2">
         <v>101</v>
       </c>
-      <c r="AI9">
+      <c r="AL9" s="11">
+        <v>153</v>
+      </c>
+      <c r="AM9">
         <v>-16.399999999999999</v>
       </c>
-      <c r="AJ9" s="2">
+      <c r="AN9" s="2">
         <v>18.55</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AO9" t="s">
         <v>131</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AP9" t="s">
         <v>132</v>
       </c>
-      <c r="AM9" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW9" t="s">
+      <c r="AQ9" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ9" s="11"/>
+      <c r="EB9" t="s">
         <v>139</v>
       </c>
-      <c r="DX9" t="s">
+      <c r="EC9" t="s">
         <v>162</v>
       </c>
-      <c r="DY9" t="s">
+      <c r="ED9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>189</v>
       </c>
       <c r="B10" t="s">
         <v>187</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>145</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>127</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>190</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>128</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>148</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>188</v>
       </c>
-      <c r="J10" s="2">
+      <c r="L10" s="2">
         <v>154</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>182</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>6</v>
       </c>
-      <c r="N10" s="2">
+      <c r="P10" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q10" s="2">
         <v>27</v>
       </c>
-      <c r="O10" s="2">
+      <c r="R10" s="2">
         <v>154</v>
       </c>
-      <c r="R10" s="2">
+      <c r="U10" s="2">
         <v>38</v>
       </c>
-      <c r="S10" s="2">
+      <c r="V10" s="2">
         <v>154</v>
       </c>
-      <c r="Z10" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE10" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC10" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF10" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI10" t="s">
         <v>130</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AJ10" s="2">
         <v>152</v>
       </c>
-      <c r="AH10" s="2">
+      <c r="AK10" s="2">
         <v>100</v>
       </c>
-      <c r="AI10">
+      <c r="AL10" s="11">
+        <v>152</v>
+      </c>
+      <c r="AM10">
         <v>-18.100000000000001</v>
       </c>
-      <c r="AJ10" s="2">
+      <c r="AN10" s="2">
         <v>18.489999999999998</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AO10" t="s">
         <v>131</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AP10" t="s">
         <v>132</v>
       </c>
-      <c r="AM10" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW10" t="s">
+      <c r="AQ10" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ10" s="11"/>
+      <c r="EB10" t="s">
         <v>139</v>
       </c>
-      <c r="DX10" t="s">
+      <c r="EC10" t="s">
         <v>162</v>
       </c>
-      <c r="DY10" t="s">
+      <c r="ED10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>163</v>
       </c>
       <c r="B11" t="s">
         <v>187</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>145</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>163</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>129</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>128</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>148</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>188</v>
       </c>
-      <c r="J11" s="2">
+      <c r="L11" s="2">
         <v>155</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>182</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>6</v>
       </c>
-      <c r="N11" s="2">
+      <c r="P11" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q11" s="2">
         <v>21</v>
       </c>
-      <c r="O11" s="2">
+      <c r="R11" s="2">
         <v>155</v>
       </c>
-      <c r="R11" s="2">
+      <c r="U11" s="2">
         <v>27</v>
       </c>
-      <c r="S11" s="2">
+      <c r="V11" s="2">
         <v>155</v>
       </c>
-      <c r="Z11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB11" s="2" t="s">
+      <c r="AC11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AC11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF11" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI11" t="s">
         <v>130</v>
       </c>
-      <c r="AG11" s="2">
+      <c r="AJ11" s="2">
         <v>155</v>
       </c>
-      <c r="AH11" s="2">
+      <c r="AK11" s="2">
         <v>100</v>
       </c>
-      <c r="AI11">
+      <c r="AL11" s="11">
+        <v>155</v>
+      </c>
+      <c r="AM11">
         <v>-14.3</v>
       </c>
-      <c r="AJ11" s="2">
+      <c r="AN11" s="2">
         <v>18.670000000000002</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AO11" t="s">
         <v>131</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AP11" t="s">
         <v>132</v>
       </c>
-      <c r="AM11" t="s">
-        <v>133</v>
-      </c>
-      <c r="DW11" t="s">
+      <c r="AQ11" t="s">
+        <v>133</v>
+      </c>
+      <c r="BZ11" s="11"/>
+      <c r="EB11" t="s">
         <v>163</v>
       </c>
-      <c r="DX11" t="s">
+      <c r="EC11" t="s">
         <v>162</v>
       </c>
-      <c r="DY11" t="s">
+      <c r="ED11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>192</v>
       </c>
       <c r="B12" t="s">
         <v>193</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>145</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>163</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>129</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>128</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>148</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>194</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>73</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>195</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>19</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>4</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q12" t="s">
         <v>151</v>
       </c>
-      <c r="O12" t="s">
+      <c r="R12" t="s">
         <v>196</v>
       </c>
-      <c r="R12" t="s">
+      <c r="U12" t="s">
         <v>197</v>
       </c>
-      <c r="S12" t="s">
+      <c r="V12" t="s">
         <v>198</v>
       </c>
-      <c r="T12" t="s">
+      <c r="W12" t="s">
         <v>151</v>
       </c>
-      <c r="U12" t="s">
+      <c r="X12" t="s">
         <v>198</v>
       </c>
-      <c r="V12" t="s">
+      <c r="Y12" t="s">
         <v>129</v>
       </c>
-      <c r="W12" t="s">
+      <c r="Z12" t="s">
         <v>196</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AA12" t="s">
         <v>166</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AB12" t="s">
         <v>196</v>
       </c>
-      <c r="Z12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE12" t="s">
         <v>158</v>
       </c>
-      <c r="AC12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE12" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI12" t="s">
         <v>130</v>
       </c>
-      <c r="AG12">
+      <c r="AJ12">
         <v>54</v>
       </c>
-      <c r="AH12">
+      <c r="AK12">
         <v>99.38</v>
       </c>
-      <c r="AI12">
+      <c r="AL12" s="11">
+        <v>72</v>
+      </c>
+      <c r="AM12">
         <v>88.69</v>
       </c>
-      <c r="AJ12">
+      <c r="AN12">
         <v>20.18</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AO12" t="s">
         <v>199</v>
       </c>
-      <c r="AL12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN12" t="s">
+      <c r="AP12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR12" t="s">
         <v>134</v>
       </c>
-      <c r="AO12">
+      <c r="AS12">
         <v>54</v>
       </c>
-      <c r="AP12">
+      <c r="AT12">
         <v>26.86</v>
       </c>
-      <c r="AQ12">
+      <c r="AU12">
         <v>23.61</v>
       </c>
-      <c r="AR12">
+      <c r="AV12">
         <v>6.64</v>
       </c>
-      <c r="AS12" t="s">
+      <c r="AW12" t="s">
         <v>199</v>
       </c>
-      <c r="AT12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV12" t="s">
+      <c r="AX12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ12" t="s">
         <v>135</v>
       </c>
-      <c r="AW12">
+      <c r="BA12">
         <v>54</v>
       </c>
-      <c r="AX12">
+      <c r="BB12">
         <v>24.1</v>
       </c>
-      <c r="AY12">
+      <c r="BC12">
         <v>22.65</v>
       </c>
-      <c r="AZ12">
+      <c r="BD12">
         <v>5.81</v>
       </c>
-      <c r="BA12" t="s">
+      <c r="BE12" t="s">
         <v>199</v>
       </c>
-      <c r="BB12" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT12" t="s">
+      <c r="BF12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX12" t="s">
         <v>200</v>
       </c>
-      <c r="BU12">
+      <c r="BY12">
         <v>54</v>
       </c>
-      <c r="BV12">
+      <c r="BZ12" s="11">
+        <v>72</v>
+      </c>
+      <c r="CA12">
         <v>11.58</v>
       </c>
-      <c r="BW12">
+      <c r="CB12">
         <v>9.56</v>
       </c>
-      <c r="BX12">
+      <c r="CC12">
         <v>4.03</v>
       </c>
-      <c r="BY12" t="s">
+      <c r="CD12" t="s">
         <v>199</v>
       </c>
-      <c r="BZ12" t="s">
-        <v>133</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS12">
+      <c r="CE12" t="s">
+        <v>133</v>
+      </c>
+      <c r="CF12" t="s">
+        <v>133</v>
+      </c>
+      <c r="CX12">
         <v>23</v>
       </c>
-      <c r="CT12">
+      <c r="CY12">
         <v>72</v>
       </c>
-      <c r="CW12">
+      <c r="DB12">
         <v>6</v>
       </c>
-      <c r="CX12">
+      <c r="DC12">
         <v>72</v>
       </c>
-      <c r="DA12">
+      <c r="DF12">
         <v>4</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>72</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>4</v>
       </c>
-      <c r="DD12">
+      <c r="DI12">
         <v>72</v>
       </c>
-      <c r="DK12">
+      <c r="DP12">
         <v>2</v>
       </c>
-      <c r="DL12">
+      <c r="DQ12">
         <v>72</v>
       </c>
-      <c r="DO12">
+      <c r="DT12">
         <v>1</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>72</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>1</v>
       </c>
-      <c r="DV12">
+      <c r="EA12">
         <v>72</v>
       </c>
-      <c r="DW12" t="s">
+      <c r="EB12" t="s">
         <v>163</v>
       </c>
-      <c r="DX12" t="s">
+      <c r="EC12" t="s">
         <v>162</v>
       </c>
-      <c r="DY12" t="s">
+      <c r="ED12" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>201</v>
       </c>
       <c r="B13" t="s">
         <v>193</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>145</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>202</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>203</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>128</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>148</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>194</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>71</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>195</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>19</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>4</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q13" t="s">
         <v>154</v>
       </c>
-      <c r="O13" t="s">
+      <c r="R13" t="s">
         <v>204</v>
       </c>
-      <c r="R13" t="s">
+      <c r="U13" t="s">
         <v>152</v>
       </c>
-      <c r="S13" t="s">
+      <c r="V13" t="s">
         <v>205</v>
       </c>
-      <c r="T13" t="s">
+      <c r="W13" t="s">
         <v>177</v>
       </c>
-      <c r="U13" t="s">
+      <c r="X13" t="s">
         <v>205</v>
       </c>
-      <c r="V13" s="5">
+      <c r="Y13" s="5">
         <v>0</v>
       </c>
-      <c r="W13" t="s">
+      <c r="Z13" t="s">
         <v>204</v>
       </c>
-      <c r="X13" s="5">
+      <c r="AA13" s="5">
         <v>2</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AB13" t="s">
         <v>204</v>
       </c>
-      <c r="Z13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE13" t="s">
         <v>158</v>
       </c>
-      <c r="AC13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE13" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI13" t="s">
         <v>130</v>
       </c>
-      <c r="AG13">
+      <c r="AJ13">
         <v>49</v>
       </c>
-      <c r="AH13">
+      <c r="AK13">
         <v>98.54</v>
       </c>
-      <c r="AI13">
+      <c r="AL13" s="11">
+        <v>65</v>
+      </c>
+      <c r="AM13">
         <v>88.94</v>
       </c>
-      <c r="AJ13">
+      <c r="AN13">
         <v>17.03</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AO13" t="s">
         <v>199</v>
       </c>
-      <c r="AL13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN13" t="s">
+      <c r="AP13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR13" t="s">
         <v>134</v>
       </c>
-      <c r="AO13">
+      <c r="AS13">
         <v>49</v>
       </c>
-      <c r="AP13">
+      <c r="AT13">
         <v>26.2</v>
       </c>
-      <c r="AQ13">
+      <c r="AU13">
         <v>23.41</v>
       </c>
-      <c r="AR13">
+      <c r="AV13">
         <v>6.14</v>
       </c>
-      <c r="AS13" t="s">
+      <c r="AW13" t="s">
         <v>199</v>
       </c>
-      <c r="AT13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV13" t="s">
+      <c r="AX13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ13" t="s">
         <v>135</v>
       </c>
-      <c r="AW13">
+      <c r="BA13">
         <v>49</v>
       </c>
-      <c r="AX13">
+      <c r="BB13">
         <v>23.65</v>
       </c>
-      <c r="AY13">
+      <c r="BC13">
         <v>21.82</v>
       </c>
-      <c r="AZ13">
+      <c r="BD13">
         <v>5.85</v>
       </c>
-      <c r="BA13" t="s">
+      <c r="BE13" t="s">
         <v>199</v>
       </c>
-      <c r="BB13" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT13" t="s">
+      <c r="BF13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX13" t="s">
         <v>200</v>
       </c>
-      <c r="BU13">
+      <c r="BY13">
         <v>49</v>
       </c>
-      <c r="BV13">
+      <c r="BZ13" s="11">
+        <v>65</v>
+      </c>
+      <c r="CA13">
         <v>12.91</v>
       </c>
-      <c r="BW13">
+      <c r="CB13">
         <v>9.8800000000000008</v>
       </c>
-      <c r="BX13">
+      <c r="CC13">
         <v>4.1500000000000004</v>
       </c>
-      <c r="BY13" t="s">
+      <c r="CD13" t="s">
         <v>199</v>
       </c>
-      <c r="BZ13" t="s">
-        <v>133</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS13">
+      <c r="CE13" t="s">
+        <v>133</v>
+      </c>
+      <c r="CF13" t="s">
+        <v>133</v>
+      </c>
+      <c r="CX13">
         <v>14</v>
       </c>
-      <c r="CT13">
+      <c r="CY13">
         <v>65</v>
       </c>
-      <c r="CW13">
+      <c r="DB13">
         <v>3</v>
       </c>
-      <c r="CX13">
+      <c r="DC13">
         <v>65</v>
       </c>
-      <c r="DA13">
+      <c r="DF13">
         <v>4</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>65</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>0</v>
       </c>
-      <c r="DD13">
+      <c r="DI13">
         <v>65</v>
       </c>
-      <c r="DK13">
+      <c r="DP13">
         <v>0</v>
       </c>
-      <c r="DL13">
+      <c r="DQ13">
         <v>65</v>
       </c>
-      <c r="DO13">
+      <c r="DT13">
         <v>3</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>65</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>2</v>
       </c>
-      <c r="DV13">
+      <c r="EA13">
         <v>65</v>
       </c>
-      <c r="DW13" t="s">
+      <c r="EB13" t="s">
         <v>139</v>
       </c>
-      <c r="DX13" t="s">
+      <c r="EC13" t="s">
         <v>162</v>
       </c>
-      <c r="DY13" t="s">
+      <c r="ED13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>206</v>
       </c>
       <c r="B14" t="s">
         <v>193</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14">
         <v>1</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>145</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>202</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>207</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>128</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>148</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>194</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>69</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>195</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>15</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>4</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q14" t="s">
         <v>151</v>
       </c>
-      <c r="O14" t="s">
+      <c r="R14" t="s">
         <v>208</v>
       </c>
-      <c r="R14" t="s">
+      <c r="U14" t="s">
         <v>152</v>
       </c>
-      <c r="S14" t="s">
+      <c r="V14" t="s">
         <v>209</v>
       </c>
-      <c r="T14" t="s">
+      <c r="W14" t="s">
         <v>154</v>
       </c>
-      <c r="U14" t="s">
+      <c r="X14" t="s">
         <v>209</v>
       </c>
-      <c r="V14" t="s">
+      <c r="Y14" t="s">
         <v>129</v>
       </c>
-      <c r="W14" t="s">
+      <c r="Z14" t="s">
         <v>208</v>
       </c>
-      <c r="X14" t="s">
+      <c r="AA14" t="s">
         <v>166</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AB14" t="s">
         <v>208</v>
       </c>
-      <c r="Z14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE14" t="s">
         <v>158</v>
       </c>
-      <c r="AC14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE14" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI14" t="s">
         <v>130</v>
       </c>
-      <c r="AG14">
+      <c r="AJ14">
         <v>51</v>
       </c>
-      <c r="AH14">
+      <c r="AK14">
         <v>100.53</v>
       </c>
-      <c r="AI14">
+      <c r="AL14" s="11">
+        <v>68</v>
+      </c>
+      <c r="AM14">
         <v>85.18</v>
       </c>
-      <c r="AJ14">
+      <c r="AN14">
         <v>17.670000000000002</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AO14" t="s">
         <v>199</v>
       </c>
-      <c r="AL14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="AP14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR14" t="s">
         <v>134</v>
       </c>
-      <c r="AO14">
+      <c r="AS14">
         <v>51</v>
       </c>
-      <c r="AP14">
+      <c r="AT14">
         <v>27.26</v>
       </c>
-      <c r="AQ14">
+      <c r="AU14">
         <v>22.22</v>
       </c>
-      <c r="AR14">
+      <c r="AV14">
         <v>6.5</v>
       </c>
-      <c r="AS14" t="s">
+      <c r="AW14" t="s">
         <v>199</v>
       </c>
-      <c r="AT14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV14" t="s">
+      <c r="AX14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ14" t="s">
         <v>135</v>
       </c>
-      <c r="AW14">
+      <c r="BA14">
         <v>51</v>
       </c>
-      <c r="AX14">
+      <c r="BB14">
         <v>24.59</v>
       </c>
-      <c r="AY14">
+      <c r="BC14">
         <v>22.53</v>
       </c>
-      <c r="AZ14">
+      <c r="BD14">
         <v>5.41</v>
       </c>
-      <c r="BA14" t="s">
+      <c r="BE14" t="s">
         <v>199</v>
       </c>
-      <c r="BB14" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT14" t="s">
+      <c r="BF14" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX14" t="s">
         <v>200</v>
       </c>
-      <c r="BU14">
+      <c r="BY14">
         <v>51</v>
       </c>
-      <c r="BV14">
+      <c r="BZ14" s="11">
+        <v>68</v>
+      </c>
+      <c r="CA14">
         <v>11.54</v>
       </c>
-      <c r="BW14">
+      <c r="CB14">
         <v>9.06</v>
       </c>
-      <c r="BX14">
+      <c r="CC14">
         <v>4.08</v>
       </c>
-      <c r="BY14" t="s">
+      <c r="CD14" t="s">
         <v>199</v>
       </c>
-      <c r="BZ14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS14">
+      <c r="CE14" t="s">
+        <v>133</v>
+      </c>
+      <c r="CF14" t="s">
+        <v>133</v>
+      </c>
+      <c r="CX14">
         <v>23</v>
       </c>
-      <c r="CT14">
+      <c r="CY14">
         <v>68</v>
       </c>
-      <c r="CW14">
+      <c r="DB14">
         <v>2</v>
       </c>
-      <c r="CX14">
+      <c r="DC14">
         <v>68</v>
       </c>
-      <c r="DA14">
+      <c r="DF14">
         <v>5</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>68</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>2</v>
       </c>
-      <c r="DD14">
+      <c r="DI14">
         <v>68</v>
       </c>
-      <c r="DK14">
+      <c r="DP14">
         <v>8</v>
       </c>
-      <c r="DL14">
+      <c r="DQ14">
         <v>68</v>
       </c>
-      <c r="DO14">
+      <c r="DT14">
         <v>5</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>68</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>0</v>
       </c>
-      <c r="DV14">
+      <c r="EA14">
         <v>68</v>
       </c>
-      <c r="DW14" t="s">
+      <c r="EB14" t="s">
         <v>139</v>
       </c>
-      <c r="DX14" t="s">
+      <c r="EC14" t="s">
         <v>162</v>
       </c>
-      <c r="DY14" t="s">
+      <c r="ED14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>210</v>
       </c>
       <c r="B15" t="s">
         <v>193</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>145</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>211</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>177</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>128</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>148</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>194</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>74</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>195</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>18</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>4</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q15" t="s">
         <v>153</v>
       </c>
-      <c r="O15" t="s">
+      <c r="R15" t="s">
         <v>205</v>
       </c>
-      <c r="R15" t="s">
+      <c r="U15" t="s">
         <v>165</v>
       </c>
-      <c r="S15" t="s">
+      <c r="V15" t="s">
         <v>212</v>
       </c>
-      <c r="T15" t="s">
+      <c r="W15" t="s">
         <v>166</v>
       </c>
-      <c r="U15" t="s">
+      <c r="X15" t="s">
         <v>212</v>
       </c>
-      <c r="V15" t="s">
+      <c r="Y15" t="s">
         <v>129</v>
       </c>
-      <c r="W15" t="s">
+      <c r="Z15" t="s">
         <v>205</v>
       </c>
-      <c r="X15" t="s">
+      <c r="AA15" t="s">
         <v>129</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AB15" t="s">
         <v>205</v>
       </c>
-      <c r="Z15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE15" t="s">
         <v>158</v>
       </c>
-      <c r="AC15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>156</v>
-      </c>
-      <c r="AE15" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AF15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI15" t="s">
         <v>130</v>
       </c>
-      <c r="AG15">
+      <c r="AJ15">
         <v>56</v>
       </c>
-      <c r="AH15">
+      <c r="AK15">
         <v>100.03</v>
       </c>
-      <c r="AI15">
+      <c r="AL15" s="11">
+        <v>71</v>
+      </c>
+      <c r="AM15">
         <v>78.040000000000006</v>
       </c>
-      <c r="AJ15">
+      <c r="AN15">
         <v>15.78</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AO15" t="s">
         <v>199</v>
       </c>
-      <c r="AL15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AN15" t="s">
+      <c r="AP15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR15" t="s">
         <v>134</v>
       </c>
-      <c r="AO15">
+      <c r="AS15">
         <v>56</v>
       </c>
-      <c r="AP15">
+      <c r="AT15">
         <v>27.49</v>
       </c>
-      <c r="AQ15">
+      <c r="AU15">
         <v>19.52</v>
       </c>
-      <c r="AR15">
+      <c r="AV15">
         <v>5.1100000000000003</v>
       </c>
-      <c r="AS15" t="s">
+      <c r="AW15" t="s">
         <v>199</v>
       </c>
-      <c r="AT15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV15" t="s">
+      <c r="AX15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY15" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ15" t="s">
         <v>135</v>
       </c>
-      <c r="AW15">
+      <c r="BA15">
         <v>56</v>
       </c>
-      <c r="AX15">
+      <c r="BB15">
         <v>23.65</v>
       </c>
-      <c r="AY15">
+      <c r="BC15">
         <v>21.45</v>
       </c>
-      <c r="AZ15">
+      <c r="BD15">
         <v>5.13</v>
       </c>
-      <c r="BA15" t="s">
+      <c r="BE15" t="s">
         <v>199</v>
       </c>
-      <c r="BB15" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC15" t="s">
-        <v>133</v>
-      </c>
-      <c r="BT15" t="s">
+      <c r="BF15" t="s">
+        <v>133</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>133</v>
+      </c>
+      <c r="BX15" t="s">
         <v>200</v>
       </c>
-      <c r="BU15">
+      <c r="BY15">
         <v>56</v>
       </c>
-      <c r="BV15">
+      <c r="BZ15" s="11">
+        <v>71</v>
+      </c>
+      <c r="CA15">
         <v>12.58</v>
       </c>
-      <c r="BW15">
+      <c r="CB15">
         <v>8.5</v>
       </c>
-      <c r="BX15">
+      <c r="CC15">
         <v>4.09</v>
       </c>
-      <c r="BY15" t="s">
+      <c r="CD15" t="s">
         <v>199</v>
       </c>
-      <c r="BZ15" t="s">
-        <v>133</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>133</v>
-      </c>
-      <c r="CS15">
+      <c r="CE15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CF15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CX15">
         <v>36</v>
       </c>
-      <c r="CT15">
+      <c r="CY15">
         <v>71</v>
       </c>
-      <c r="CW15">
+      <c r="DB15">
         <v>5</v>
       </c>
-      <c r="CX15">
+      <c r="DC15">
         <v>71</v>
       </c>
-      <c r="DA15">
+      <c r="DF15">
         <v>6</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>71</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>6</v>
       </c>
-      <c r="DD15">
+      <c r="DI15">
         <v>71</v>
       </c>
-      <c r="DK15">
+      <c r="DP15">
         <v>0</v>
       </c>
-      <c r="DL15">
+      <c r="DQ15">
         <v>71</v>
       </c>
-      <c r="DO15">
+      <c r="DT15">
         <v>5</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>71</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>8</v>
       </c>
-      <c r="DV15">
+      <c r="EA15">
         <v>71</v>
       </c>
-      <c r="DW15" t="s">
+      <c r="EB15" t="s">
         <v>213</v>
       </c>
-      <c r="DX15" t="s">
+      <c r="EC15" t="s">
         <v>162</v>
       </c>
-      <c r="DY15" t="s">
+      <c r="ED15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>214</v>
       </c>
       <c r="B16" t="s">
         <v>215</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>145</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>163</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>129</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>216</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>217</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>34</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>218</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>18</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R16" t="s">
+      <c r="P16" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U16" t="s">
         <v>155</v>
       </c>
-      <c r="S16" t="s">
+      <c r="V16" t="s">
         <v>219</v>
       </c>
-      <c r="T16" t="s">
+      <c r="W16" t="s">
         <v>129</v>
       </c>
-      <c r="U16" t="s">
+      <c r="X16" t="s">
         <v>219</v>
       </c>
-      <c r="V16" t="s">
+      <c r="Y16" t="s">
         <v>129</v>
       </c>
-      <c r="W16" t="s">
+      <c r="Z16" t="s">
         <v>219</v>
       </c>
-      <c r="X16" t="s">
+      <c r="AA16" t="s">
         <v>129</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AB16" t="s">
         <v>219</v>
       </c>
-      <c r="CS16">
+      <c r="AL16" s="11"/>
+      <c r="BZ16" s="11"/>
+      <c r="CX16">
         <v>16</v>
       </c>
-      <c r="CT16">
+      <c r="CY16">
         <v>34</v>
       </c>
-      <c r="CU16">
+      <c r="CZ16">
         <v>0</v>
       </c>
-      <c r="CV16">
+      <c r="DA16">
         <v>34</v>
       </c>
-      <c r="CW16">
+      <c r="DB16">
         <v>0</v>
       </c>
-      <c r="CX16">
+      <c r="DC16">
         <v>34</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>2</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>34</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>7</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>34</v>
       </c>
-      <c r="DC16">
+      <c r="DH16">
         <v>0</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>34</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>5</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>34</v>
       </c>
-      <c r="DW16" t="s">
+      <c r="EB16" t="s">
         <v>163</v>
       </c>
-      <c r="DX16" t="s">
+      <c r="EC16" t="s">
         <v>220</v>
       </c>
-      <c r="DY16" t="s">
+      <c r="ED16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>221</v>
       </c>
       <c r="B17" t="s">
         <v>215</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>145</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>127</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>180</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>216</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>217</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>35</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>222</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>14</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R17" t="s">
+      <c r="P17" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U17" t="s">
         <v>154</v>
       </c>
-      <c r="S17" t="s">
+      <c r="V17" t="s">
         <v>223</v>
       </c>
-      <c r="T17" t="s">
+      <c r="W17" t="s">
         <v>129</v>
       </c>
-      <c r="U17" t="s">
+      <c r="X17" t="s">
         <v>223</v>
       </c>
-      <c r="V17" t="s">
+      <c r="Y17" t="s">
         <v>129</v>
       </c>
-      <c r="W17" t="s">
+      <c r="Z17" t="s">
         <v>223</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AA17" t="s">
         <v>166</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AB17" t="s">
         <v>223</v>
       </c>
-      <c r="CS17">
+      <c r="AL17" s="11"/>
+      <c r="BZ17" s="11"/>
+      <c r="CX17">
         <v>34</v>
       </c>
-      <c r="CT17">
+      <c r="CY17">
         <v>35</v>
       </c>
-      <c r="CU17">
+      <c r="CZ17">
         <v>5</v>
       </c>
-      <c r="CV17">
+      <c r="DA17">
         <v>35</v>
       </c>
-      <c r="CW17">
+      <c r="DB17">
         <v>0</v>
       </c>
-      <c r="CX17">
+      <c r="DC17">
         <v>35</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>10</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>35</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>4</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>35</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>12</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>35</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>21</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>35</v>
       </c>
-      <c r="DW17" t="s">
+      <c r="EB17" t="s">
         <v>139</v>
       </c>
-      <c r="DX17" t="s">
+      <c r="EC17" t="s">
         <v>220</v>
       </c>
-      <c r="DY17" t="s">
+      <c r="ED17" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:129" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>224</v>
       </c>
       <c r="B18" t="s">
         <v>215</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>145</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>225</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>226</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>216</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>217</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>36</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18" t="s">
         <v>227</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>13</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R18" t="s">
+      <c r="P18" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U18" t="s">
         <v>155</v>
       </c>
-      <c r="S18" t="s">
+      <c r="V18" t="s">
         <v>228</v>
       </c>
-      <c r="T18" t="s">
+      <c r="W18" t="s">
         <v>129</v>
       </c>
-      <c r="U18" t="s">
+      <c r="X18" t="s">
         <v>228</v>
       </c>
-      <c r="V18" t="s">
+      <c r="Y18" t="s">
         <v>129</v>
       </c>
-      <c r="W18" t="s">
+      <c r="Z18" t="s">
         <v>228</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AA18" t="s">
         <v>129</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AB18" t="s">
         <v>228</v>
       </c>
-      <c r="CS18">
+      <c r="AL18" s="11"/>
+      <c r="BZ18" s="11"/>
+      <c r="CX18">
         <v>15</v>
       </c>
-      <c r="CT18">
+      <c r="CY18">
         <v>36</v>
       </c>
-      <c r="CU18">
+      <c r="CZ18">
         <v>0</v>
       </c>
-      <c r="CV18">
+      <c r="DA18">
         <v>36</v>
       </c>
-      <c r="CW18">
+      <c r="DB18">
         <v>3</v>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>36</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>1</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>36</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>1</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>36</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>0</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>36</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>5</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>36</v>
       </c>
-      <c r="DW18" t="s">
+      <c r="EB18" t="s">
         <v>213</v>
       </c>
-      <c r="DX18" t="s">
+      <c r="EC18" t="s">
         <v>220</v>
       </c>
-      <c r="DY18" t="s">
+      <c r="ED18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>163</v>
       </c>
       <c r="B19" t="s">
         <v>229</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>230</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>163</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>129</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>128</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>231</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>208</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>68</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>232</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>15</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>0.14000000000000001</v>
       </c>
-      <c r="T19" t="s">
+      <c r="P19" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="W19" t="s">
         <v>166</v>
       </c>
-      <c r="U19" t="s">
+      <c r="X19" t="s">
         <v>233</v>
       </c>
-      <c r="V19" t="s">
+      <c r="Y19" t="s">
         <v>129</v>
       </c>
-      <c r="W19" t="s">
+      <c r="Z19" t="s">
         <v>233</v>
       </c>
-      <c r="X19" t="s">
+      <c r="AA19" t="s">
         <v>129</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AB19" t="s">
         <v>233</v>
       </c>
-      <c r="CS19">
+      <c r="AL19" s="11"/>
+      <c r="BZ19" s="11"/>
+      <c r="CX19">
         <v>2</v>
       </c>
-      <c r="CT19">
+      <c r="CY19">
         <v>63</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>1</v>
       </c>
-      <c r="CZ19">
+      <c r="DE19">
         <v>63</v>
       </c>
-      <c r="DC19">
+      <c r="DH19">
         <v>1</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>63</v>
       </c>
-      <c r="DE19" s="8">
+      <c r="DJ19" s="8">
         <v>0</v>
       </c>
-      <c r="DF19">
+      <c r="DK19">
         <v>63</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>1</v>
       </c>
-      <c r="DJ19">
+      <c r="DO19">
         <v>59</v>
       </c>
-      <c r="DW19" t="s">
+      <c r="EB19" t="s">
         <v>163</v>
       </c>
-      <c r="DX19" t="s">
+      <c r="EC19" t="s">
         <v>220</v>
       </c>
-      <c r="DY19" t="s">
+      <c r="ED19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>234</v>
       </c>
       <c r="B20" t="s">
         <v>229</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>230</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>127</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>207</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>128</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>231</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>208</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>68</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>232</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>15</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R20" t="s">
+      <c r="P20" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U20" t="s">
         <v>129</v>
       </c>
-      <c r="S20" t="s">
+      <c r="V20" t="s">
         <v>233</v>
       </c>
-      <c r="T20" t="s">
+      <c r="W20" t="s">
         <v>129</v>
       </c>
-      <c r="U20" t="s">
+      <c r="X20" t="s">
         <v>233</v>
       </c>
-      <c r="V20" t="s">
+      <c r="Y20" t="s">
         <v>129</v>
       </c>
-      <c r="W20" t="s">
+      <c r="Z20" t="s">
         <v>233</v>
       </c>
-      <c r="X20" t="s">
+      <c r="AA20" t="s">
         <v>166</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AB20" t="s">
         <v>233</v>
       </c>
-      <c r="CS20">
+      <c r="AL20" s="11"/>
+      <c r="BZ20" s="11"/>
+      <c r="CX20">
         <v>32</v>
       </c>
-      <c r="CT20">
+      <c r="CY20">
         <v>63</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>7</v>
       </c>
-      <c r="CZ20">
+      <c r="DE20">
         <v>63</v>
       </c>
-      <c r="DC20">
+      <c r="DH20">
         <v>16</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>63</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>16</v>
       </c>
-      <c r="DF20">
+      <c r="DK20">
         <v>63</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>5</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>62</v>
       </c>
-      <c r="DW20" t="s">
+      <c r="EB20" t="s">
         <v>139</v>
       </c>
-      <c r="DX20" t="s">
+      <c r="EC20" t="s">
         <v>220</v>
       </c>
-      <c r="DY20" t="s">
+      <c r="ED20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>235</v>
       </c>
       <c r="B21" t="s">
         <v>236</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="11">
+        <v>2021</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21">
         <v>1</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>230</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>127</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>153</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>216</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>191</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>12</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>237</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>0</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R21" t="s">
+      <c r="P21" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U21" t="s">
         <v>129</v>
       </c>
-      <c r="S21" t="s">
+      <c r="V21" t="s">
         <v>141</v>
       </c>
-      <c r="T21" t="s">
+      <c r="W21" t="s">
         <v>129</v>
       </c>
-      <c r="U21" t="s">
+      <c r="X21" t="s">
         <v>141</v>
       </c>
-      <c r="V21" t="s">
+      <c r="Y21" t="s">
         <v>129</v>
       </c>
-      <c r="W21" t="s">
+      <c r="Z21" t="s">
         <v>141</v>
       </c>
-      <c r="X21" t="s">
+      <c r="AA21" t="s">
         <v>129</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AB21" t="s">
         <v>141</v>
       </c>
-      <c r="CS21">
+      <c r="AL21" s="11"/>
+      <c r="BZ21" s="11"/>
+      <c r="CX21">
         <v>1</v>
       </c>
-      <c r="CT21">
+      <c r="CY21">
         <v>12</v>
       </c>
-      <c r="DC21">
+      <c r="DH21">
         <v>1</v>
       </c>
-      <c r="DD21">
+      <c r="DI21">
         <v>12</v>
       </c>
-      <c r="DE21">
+      <c r="DJ21">
         <v>0</v>
       </c>
-      <c r="DF21">
+      <c r="DK21">
         <v>12</v>
       </c>
-      <c r="DG21">
+      <c r="DL21">
         <v>0</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>12</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>0</v>
       </c>
-      <c r="DJ21">
+      <c r="DO21">
         <v>12</v>
       </c>
-      <c r="DW21" t="s">
+      <c r="EB21" t="s">
         <v>139</v>
       </c>
-      <c r="DX21" t="s">
+      <c r="EC21" t="s">
         <v>220</v>
       </c>
-      <c r="DY21" t="s">
+      <c r="ED21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>238</v>
       </c>
       <c r="B22" t="s">
         <v>236</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="11">
+        <v>2021</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22">
         <v>1</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>230</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>127</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>180</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>216</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>191</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>12</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>237</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>0</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R22" t="s">
+      <c r="P22" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U22" t="s">
         <v>129</v>
       </c>
-      <c r="S22" t="s">
+      <c r="V22" t="s">
         <v>141</v>
       </c>
-      <c r="T22" t="s">
+      <c r="W22" t="s">
         <v>129</v>
       </c>
-      <c r="U22" t="s">
+      <c r="X22" t="s">
         <v>141</v>
       </c>
-      <c r="V22" t="s">
+      <c r="Y22" t="s">
         <v>129</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Z22" t="s">
         <v>141</v>
       </c>
-      <c r="X22" t="s">
+      <c r="AA22" t="s">
         <v>129</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AB22" t="s">
         <v>141</v>
       </c>
-      <c r="CS22">
+      <c r="AL22" s="11"/>
+      <c r="BZ22" s="11"/>
+      <c r="CX22">
         <v>1</v>
       </c>
-      <c r="CT22">
+      <c r="CY22">
         <v>12</v>
       </c>
-      <c r="DC22">
+      <c r="DH22">
         <v>0</v>
       </c>
-      <c r="DD22">
+      <c r="DI22">
         <v>12</v>
       </c>
-      <c r="DE22">
+      <c r="DJ22">
         <v>1</v>
       </c>
-      <c r="DF22">
+      <c r="DK22">
         <v>12</v>
       </c>
-      <c r="DG22">
+      <c r="DL22">
         <v>0</v>
       </c>
-      <c r="DH22">
+      <c r="DM22">
         <v>12</v>
       </c>
-      <c r="DI22">
+      <c r="DN22">
         <v>0</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>12</v>
       </c>
-      <c r="DW22" t="s">
+      <c r="EB22" t="s">
         <v>139</v>
       </c>
-      <c r="DX22" t="s">
+      <c r="EC22" t="s">
         <v>220</v>
       </c>
-      <c r="DY22" t="s">
+      <c r="ED22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>163</v>
       </c>
       <c r="B23" t="s">
         <v>236</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="11">
+        <v>2021</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>230</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>163</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>129</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>216</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>191</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>24</v>
       </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
         <v>237</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>0.14000000000000001</v>
       </c>
-      <c r="R23" t="s">
+      <c r="P23" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="U23" t="s">
         <v>129</v>
       </c>
-      <c r="S23" t="s">
+      <c r="V23" t="s">
         <v>191</v>
       </c>
-      <c r="T23" t="s">
+      <c r="W23" t="s">
         <v>129</v>
       </c>
-      <c r="U23" t="s">
+      <c r="X23" t="s">
         <v>191</v>
       </c>
-      <c r="V23" t="s">
+      <c r="Y23" t="s">
         <v>129</v>
       </c>
-      <c r="W23" t="s">
+      <c r="Z23" t="s">
         <v>191</v>
       </c>
-      <c r="X23" t="s">
+      <c r="AA23" t="s">
         <v>129</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="AB23" t="s">
         <v>191</v>
       </c>
-      <c r="CS23">
+      <c r="AL23" s="11"/>
+      <c r="BZ23" s="11"/>
+      <c r="CX23">
         <v>1</v>
       </c>
-      <c r="CT23">
+      <c r="CY23">
         <v>24</v>
       </c>
-      <c r="DC23">
+      <c r="DH23">
         <v>0</v>
       </c>
-      <c r="DD23">
+      <c r="DI23">
         <v>24</v>
       </c>
-      <c r="DE23">
+      <c r="DJ23">
         <v>0</v>
       </c>
-      <c r="DF23">
+      <c r="DK23">
         <v>24</v>
       </c>
-      <c r="DG23">
+      <c r="DL23">
         <v>0</v>
       </c>
-      <c r="DH23">
+      <c r="DM23">
         <v>24</v>
       </c>
-      <c r="DI23">
+      <c r="DN23">
         <v>0</v>
       </c>
-      <c r="DJ23">
+      <c r="DO23">
         <v>24</v>
       </c>
-      <c r="DW23" t="s">
+      <c r="EB23" t="s">
         <v>163</v>
       </c>
-      <c r="DX23" t="s">
+      <c r="EC23" t="s">
         <v>220</v>
       </c>
-      <c r="DY23" t="s">
+      <c r="ED23" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>238</v>
       </c>
       <c r="B24" t="s">
         <v>239</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>230</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>127</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>180</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>240</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>152</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>16</v>
       </c>
-      <c r="K24" t="s">
+      <c r="M24" t="s">
         <v>241</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>12</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>2</v>
       </c>
-      <c r="V24" t="s">
+      <c r="P24" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y24" t="s">
         <v>129</v>
       </c>
-      <c r="W24" t="s">
+      <c r="Z24" t="s">
         <v>152</v>
       </c>
-      <c r="X24" t="s">
+      <c r="AA24" t="s">
         <v>129</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AB24" t="s">
         <v>152</v>
       </c>
-      <c r="CS24" s="6">
+      <c r="AL24" s="11"/>
+      <c r="BZ24" s="11"/>
+      <c r="CX24" s="6">
         <v>6</v>
       </c>
-      <c r="CT24" s="6">
+      <c r="CY24" s="6">
         <v>15</v>
       </c>
-      <c r="DW24" t="s">
+      <c r="EB24" t="s">
         <v>139</v>
       </c>
-      <c r="DX24" t="s">
+      <c r="EC24" t="s">
         <v>220</v>
       </c>
-      <c r="DY24" t="s">
+      <c r="ED24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>242</v>
       </c>
       <c r="B25" t="s">
         <v>239</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>230</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>127</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>142</v>
       </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>240</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>152</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>16</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>241</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>12</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>2</v>
       </c>
-      <c r="V25" t="s">
+      <c r="P25" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y25" t="s">
         <v>129</v>
       </c>
-      <c r="W25" t="s">
+      <c r="Z25" t="s">
         <v>152</v>
       </c>
-      <c r="X25" t="s">
+      <c r="AA25" t="s">
         <v>129</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AB25" t="s">
         <v>152</v>
       </c>
-      <c r="CS25" s="6">
+      <c r="AL25" s="11"/>
+      <c r="BZ25" s="11"/>
+      <c r="CX25" s="6">
         <v>1</v>
       </c>
-      <c r="CT25" s="6">
+      <c r="CY25" s="6">
         <v>13</v>
       </c>
-      <c r="DW25" t="s">
+      <c r="EB25" t="s">
         <v>139</v>
       </c>
-      <c r="DX25" t="s">
+      <c r="EC25" t="s">
         <v>220</v>
       </c>
-      <c r="DY25" t="s">
+      <c r="ED25" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:129" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>163</v>
       </c>
       <c r="B26" t="s">
         <v>239</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="11">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>230</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>163</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>129</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>240</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>152</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>16</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>241</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>12</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2</v>
       </c>
-      <c r="V26" t="s">
+      <c r="P26" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y26" t="s">
         <v>129</v>
       </c>
-      <c r="W26" t="s">
+      <c r="Z26" t="s">
         <v>152</v>
       </c>
-      <c r="X26" t="s">
+      <c r="AA26" t="s">
         <v>129</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AB26" t="s">
         <v>152</v>
       </c>
-      <c r="CS26" s="6">
+      <c r="AL26" s="11"/>
+      <c r="BZ26" s="11"/>
+      <c r="CX26" s="6">
         <v>2</v>
       </c>
-      <c r="CT26" s="6">
+      <c r="CY26" s="6">
         <v>14</v>
       </c>
-      <c r="DW26" t="s">
+      <c r="EB26" t="s">
         <v>163</v>
       </c>
-      <c r="DX26" t="s">
+      <c r="EC26" t="s">
         <v>220</v>
       </c>
-      <c r="DY26" t="s">
+      <c r="ED26" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D26" r:id="rId1" xr:uid="{3ACBAB31-28B9-454E-95A4-F4639A9A67ED}"/>
+    <hyperlink ref="D25" r:id="rId2" xr:uid="{FE0E719C-1299-FD4B-BBEB-76742ECF8E12}"/>
+    <hyperlink ref="D24" r:id="rId3" xr:uid="{F843FABE-8A54-234D-9900-E49F5856B669}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{010C7D8E-424F-B242-9FE6-6EFED4084E4E}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{2EBEE840-8777-DE4D-ABDE-6958FAF97144}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{014B3B65-1DC5-0C49-981E-21FAC2BE8F30}"/>
+    <hyperlink ref="D19" r:id="rId7" xr:uid="{AB0D1AD1-FCA2-6F4E-9E8E-0CCBD71F462D}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{1A548117-080B-8C47-947F-F1708D790B33}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/LSR3_H_2024-01-22.xlsx
+++ b/data/LSR3_H_2024-01-22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF850F3-35FC-C94E-970A-B4DD60DA6D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28467886-B497-1C40-8AE1-701134C60F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21080" yWindow="-17900" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16860" yWindow="-20160" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="262">
   <si>
     <t>arm_name</t>
   </si>
@@ -803,6 +803,21 @@
   </si>
   <si>
     <t>depression_baseline_n</t>
+  </si>
+  <si>
+    <t>cognition_baseline_n</t>
+  </si>
+  <si>
+    <t>positive_baseline_n</t>
+  </si>
+  <si>
+    <t>negative_baseline_n</t>
+  </si>
+  <si>
+    <t>weight_baseline_n</t>
+  </si>
+  <si>
+    <t>prolactin_baseline_n</t>
   </si>
 </sst>
 </file>
@@ -1222,16 +1237,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ED26"/>
+  <dimension ref="A1:EI26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" customWidth="1"/>
     <col min="15" max="16" width="9" customWidth="1"/>
     <col min="37" max="38" width="12.83203125" customWidth="1"/>
+    <col min="46" max="46" width="8.83203125" style="11"/>
+    <col min="54" max="54" width="8.83203125" style="11"/>
+    <col min="72" max="72" width="8.83203125" style="11"/>
+    <col min="90" max="90" width="8.83203125" style="11"/>
+    <col min="100" max="100" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:139" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1367,275 +1387,290 @@
       <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BZ1" s="10" t="s">
+      <c r="CC1" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CL1" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="CM1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CV1" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="CW1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="CZ1" s="7" t="s">
+      <c r="DE1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="DA1" s="7" t="s">
+      <c r="DF1" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DY1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DZ1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="EA1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="EB1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="DX1" s="1" t="s">
+      <c r="EC1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="DY1" s="1" t="s">
+      <c r="ED1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="DZ1" s="1" t="s">
+      <c r="EE1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="EA1" s="1" t="s">
+      <c r="EF1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="EB1" s="1" t="s">
+      <c r="EG1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="EC1" s="1" t="s">
+      <c r="EH1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="ED1" s="1" t="s">
+      <c r="EI1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -1760,97 +1795,103 @@
       <c r="AS2">
         <v>24</v>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="11">
+        <v>24</v>
+      </c>
+      <c r="AU2">
         <v>13.1</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>-2.5</v>
       </c>
-      <c r="AV2">
+      <c r="AW2">
         <v>7.94</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>131</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>132</v>
       </c>
-      <c r="AY2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="AZ2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BR2" t="s">
         <v>161</v>
       </c>
-      <c r="BQ2">
+      <c r="BS2">
         <v>23</v>
       </c>
-      <c r="BR2">
+      <c r="BT2" s="11">
+        <v>24</v>
+      </c>
+      <c r="BU2">
         <v>-25.1</v>
       </c>
-      <c r="BS2">
+      <c r="BV2">
         <v>0.8</v>
       </c>
-      <c r="BT2">
+      <c r="BW2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BX2" t="s">
         <v>131</v>
       </c>
-      <c r="BV2" t="s">
+      <c r="BY2" t="s">
         <v>132</v>
       </c>
-      <c r="BW2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BZ2" s="11"/>
-      <c r="CX2">
+      <c r="BZ2" t="s">
+        <v>133</v>
+      </c>
+      <c r="CC2" s="11"/>
+      <c r="DC2">
         <v>18</v>
       </c>
-      <c r="CY2">
+      <c r="DD2">
         <v>25</v>
       </c>
-      <c r="DB2" s="9"/>
-      <c r="DC2" s="9"/>
-      <c r="DD2">
+      <c r="DG2" s="9"/>
+      <c r="DH2" s="9"/>
+      <c r="DI2">
         <v>4</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>25</v>
       </c>
-      <c r="DH2">
+      <c r="DM2">
         <v>3</v>
       </c>
-      <c r="DI2">
+      <c r="DN2">
         <v>25</v>
       </c>
-      <c r="DJ2">
+      <c r="DO2">
         <v>2</v>
       </c>
-      <c r="DK2">
+      <c r="DP2">
         <v>25</v>
       </c>
-      <c r="DP2" s="9"/>
-      <c r="DQ2" s="9"/>
-      <c r="DR2">
+      <c r="DU2" s="9"/>
+      <c r="DV2" s="9"/>
+      <c r="DW2">
         <v>13</v>
       </c>
-      <c r="DS2">
+      <c r="DX2">
         <v>25</v>
       </c>
-      <c r="DT2" s="8">
+      <c r="DY2" s="8">
         <v>2</v>
       </c>
-      <c r="EB2" t="s">
+      <c r="EG2" t="s">
         <v>139</v>
       </c>
-      <c r="EC2" t="s">
+      <c r="EH2" t="s">
         <v>162</v>
       </c>
-      <c r="ED2" t="s">
+      <c r="EI2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -1975,108 +2016,114 @@
       <c r="AS3">
         <v>14</v>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="11">
+        <v>14</v>
+      </c>
+      <c r="AU3">
         <v>14.7</v>
       </c>
-      <c r="AU3">
+      <c r="AV3">
         <v>-1.4</v>
       </c>
-      <c r="AV3">
+      <c r="AW3">
         <v>7.71</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>131</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>132</v>
       </c>
-      <c r="AY3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BP3" t="s">
+      <c r="AZ3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BR3" t="s">
         <v>161</v>
       </c>
-      <c r="BQ3">
+      <c r="BS3">
         <v>14</v>
       </c>
-      <c r="BR3">
+      <c r="BT3" s="11">
+        <v>14</v>
+      </c>
+      <c r="BU3">
         <v>-24.7</v>
       </c>
-      <c r="BS3">
+      <c r="BV3">
         <v>-0.3</v>
       </c>
-      <c r="BT3">
+      <c r="BW3">
         <v>1.99</v>
       </c>
-      <c r="BU3" t="s">
+      <c r="BX3" t="s">
         <v>131</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BY3" t="s">
         <v>132</v>
       </c>
-      <c r="BW3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BZ3" s="11"/>
-      <c r="CX3">
+      <c r="BZ3" t="s">
+        <v>133</v>
+      </c>
+      <c r="CC3" s="11"/>
+      <c r="DC3">
         <v>12</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>14</v>
       </c>
-      <c r="DB3">
+      <c r="DG3">
         <v>0</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>14</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>1</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>14</v>
       </c>
-      <c r="DH3">
+      <c r="DM3">
         <v>1</v>
       </c>
-      <c r="DI3">
+      <c r="DN3">
         <v>14</v>
       </c>
-      <c r="DJ3">
+      <c r="DO3">
         <v>2</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>14</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>1</v>
       </c>
-      <c r="DQ3">
+      <c r="DV3">
         <v>14</v>
       </c>
-      <c r="DR3">
+      <c r="DW3">
         <v>11</v>
       </c>
-      <c r="DS3">
+      <c r="DX3">
         <v>14</v>
       </c>
-      <c r="DT3">
+      <c r="DY3">
         <v>1</v>
       </c>
-      <c r="DU3">
+      <c r="DZ3">
         <v>14</v>
       </c>
-      <c r="EB3" t="s">
+      <c r="EG3" t="s">
         <v>163</v>
       </c>
-      <c r="EC3" t="s">
+      <c r="EH3" t="s">
         <v>162</v>
       </c>
-      <c r="ED3" t="s">
+      <c r="EI3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -2206,200 +2253,209 @@
       <c r="AS4">
         <v>120</v>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="11">
+        <v>120</v>
+      </c>
+      <c r="AU4">
         <v>25.8</v>
       </c>
-      <c r="AU4">
+      <c r="AV4">
         <v>-5.5</v>
       </c>
-      <c r="AV4">
+      <c r="AW4">
         <v>5.48</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>131</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>132</v>
       </c>
-      <c r="AY4" t="s">
-        <v>133</v>
-      </c>
       <c r="AZ4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA4" t="s">
         <v>135</v>
       </c>
-      <c r="BA4">
+      <c r="BB4" s="11">
         <v>120</v>
       </c>
-      <c r="BB4">
+      <c r="BC4">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>24.7</v>
       </c>
-      <c r="BC4">
+      <c r="BE4">
         <v>-3.1</v>
       </c>
-      <c r="BD4">
+      <c r="BF4">
         <v>4.38</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BG4" t="s">
         <v>131</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BH4" t="s">
         <v>132</v>
       </c>
-      <c r="BG4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX4" t="s">
+      <c r="BI4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA4" t="s">
         <v>136</v>
       </c>
-      <c r="BY4">
+      <c r="CB4">
         <v>120</v>
       </c>
-      <c r="BZ4" s="11">
+      <c r="CC4" s="11">
         <v>120</v>
       </c>
-      <c r="CA4">
+      <c r="CD4">
         <v>13.1</v>
       </c>
-      <c r="CB4">
+      <c r="CE4">
         <v>-3.3</v>
       </c>
-      <c r="CC4">
+      <c r="CF4">
         <v>6.57</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CG4" t="s">
         <v>131</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CH4" t="s">
         <v>132</v>
       </c>
-      <c r="CF4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CG4" t="s">
+      <c r="CI4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ4" t="s">
         <v>137</v>
       </c>
-      <c r="CH4">
+      <c r="CK4">
         <v>120</v>
       </c>
-      <c r="CI4">
+      <c r="CL4" s="11">
+        <v>120</v>
+      </c>
+      <c r="CM4">
         <v>75.400000000000006</v>
       </c>
-      <c r="CJ4">
+      <c r="CN4">
         <v>0.3</v>
       </c>
-      <c r="CK4">
+      <c r="CO4">
         <v>1.9</v>
       </c>
-      <c r="CL4" t="s">
+      <c r="CP4" t="s">
         <v>131</v>
       </c>
-      <c r="CM4" t="s">
+      <c r="CQ4" t="s">
         <v>132</v>
       </c>
-      <c r="CN4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CO4" t="s">
+      <c r="CR4" t="s">
+        <v>133</v>
+      </c>
+      <c r="CS4" t="s">
         <v>173</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CT4" t="s">
         <v>138</v>
       </c>
-      <c r="CQ4">
+      <c r="CU4">
         <v>114</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>28</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CZ4" t="s">
         <v>131</v>
       </c>
-      <c r="CV4" t="s">
-        <v>133</v>
-      </c>
-      <c r="CW4" t="s">
+      <c r="DA4" t="s">
+        <v>133</v>
+      </c>
+      <c r="DB4" t="s">
         <v>132</v>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>55</v>
       </c>
-      <c r="CY4">
+      <c r="DD4">
         <v>120</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>2</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>120</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>11</v>
       </c>
-      <c r="DG4">
+      <c r="DL4">
         <v>120</v>
       </c>
-      <c r="DH4">
+      <c r="DM4">
         <v>6</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>120</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>8</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>120</v>
       </c>
-      <c r="DN4">
+      <c r="DS4">
         <v>0</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>120</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>6</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>120</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>4</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>120</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>1</v>
       </c>
-      <c r="DW4">
+      <c r="EB4">
         <v>120</v>
       </c>
-      <c r="DX4">
+      <c r="EC4">
         <v>4</v>
       </c>
-      <c r="DY4">
+      <c r="ED4">
         <v>120</v>
       </c>
-      <c r="DZ4">
+      <c r="EE4">
         <v>1</v>
       </c>
-      <c r="EA4">
+      <c r="EF4">
         <v>120</v>
       </c>
-      <c r="EB4" t="s">
+      <c r="EG4" t="s">
         <v>139</v>
       </c>
-      <c r="EC4" t="s">
+      <c r="EH4" t="s">
         <v>162</v>
       </c>
-      <c r="ED4" t="s">
+      <c r="EI4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>163</v>
       </c>
@@ -2529,200 +2585,209 @@
       <c r="AS5">
         <v>125</v>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="11">
+        <v>125</v>
+      </c>
+      <c r="AU5">
         <v>25.4</v>
       </c>
-      <c r="AU5">
+      <c r="AV5">
         <v>-3.9</v>
       </c>
-      <c r="AV5">
+      <c r="AW5">
         <v>5.59</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>131</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>132</v>
       </c>
-      <c r="AY5" t="s">
-        <v>133</v>
-      </c>
       <c r="AZ5" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA5" t="s">
         <v>135</v>
       </c>
-      <c r="BA5">
+      <c r="BB5" s="11">
         <v>125</v>
       </c>
-      <c r="BB5">
+      <c r="BC5">
+        <v>125</v>
+      </c>
+      <c r="BD5">
         <v>24.9</v>
       </c>
-      <c r="BC5">
+      <c r="BE5">
         <v>-1.6</v>
       </c>
-      <c r="BD5">
+      <c r="BF5">
         <v>4.47</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BG5" t="s">
         <v>131</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BH5" t="s">
         <v>132</v>
       </c>
-      <c r="BG5" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX5" t="s">
+      <c r="BI5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA5" t="s">
         <v>136</v>
       </c>
-      <c r="BY5">
+      <c r="CB5">
         <v>125</v>
       </c>
-      <c r="BZ5" s="11">
+      <c r="CC5" s="11">
         <v>125</v>
       </c>
-      <c r="CA5">
+      <c r="CD5">
         <v>12.6</v>
       </c>
-      <c r="CB5">
+      <c r="CE5">
         <v>-1.6</v>
       </c>
-      <c r="CC5">
+      <c r="CF5">
         <v>6.71</v>
       </c>
-      <c r="CD5" t="s">
+      <c r="CG5" t="s">
         <v>131</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CH5" t="s">
         <v>132</v>
       </c>
-      <c r="CF5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CG5" t="s">
+      <c r="CI5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ5" t="s">
         <v>137</v>
       </c>
-      <c r="CH5">
+      <c r="CK5">
         <v>125</v>
       </c>
-      <c r="CI5">
+      <c r="CL5" s="11">
+        <v>125</v>
+      </c>
+      <c r="CM5">
         <v>75.400000000000006</v>
       </c>
-      <c r="CJ5">
+      <c r="CN5">
         <v>-0.1</v>
       </c>
-      <c r="CK5">
+      <c r="CO5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="CL5" t="s">
+      <c r="CP5" t="s">
         <v>131</v>
       </c>
-      <c r="CM5" t="s">
+      <c r="CQ5" t="s">
         <v>132</v>
       </c>
-      <c r="CN5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CO5" t="s">
+      <c r="CR5" t="s">
+        <v>133</v>
+      </c>
+      <c r="CS5" t="s">
         <v>173</v>
       </c>
-      <c r="CP5" t="s">
+      <c r="CT5" t="s">
         <v>138</v>
       </c>
-      <c r="CQ5">
+      <c r="CU5">
         <v>113</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>-1.3838053097345131</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>28</v>
       </c>
-      <c r="CU5" t="s">
+      <c r="CZ5" t="s">
         <v>131</v>
       </c>
-      <c r="CV5" t="s">
-        <v>133</v>
-      </c>
-      <c r="CW5" t="s">
+      <c r="DA5" t="s">
+        <v>133</v>
+      </c>
+      <c r="DB5" t="s">
         <v>132</v>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>63</v>
       </c>
-      <c r="CY5">
+      <c r="DD5">
         <v>125</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>9</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>125</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>15</v>
       </c>
-      <c r="DG5">
+      <c r="DL5">
         <v>125</v>
       </c>
-      <c r="DH5">
+      <c r="DM5">
         <v>4</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>125</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>6</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>125</v>
       </c>
-      <c r="DN5">
+      <c r="DS5">
         <v>0</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>125</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>6</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>125</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>13</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>125</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>0</v>
       </c>
-      <c r="DW5">
+      <c r="EB5">
         <v>125</v>
       </c>
-      <c r="DX5">
+      <c r="EC5">
         <v>4</v>
       </c>
-      <c r="DY5">
+      <c r="ED5">
         <v>125</v>
       </c>
-      <c r="DZ5">
+      <c r="EE5">
         <v>1</v>
       </c>
-      <c r="EA5">
+      <c r="EF5">
         <v>125</v>
       </c>
-      <c r="EB5" t="s">
+      <c r="EG5" t="s">
         <v>163</v>
       </c>
-      <c r="EC5" t="s">
+      <c r="EH5" t="s">
         <v>162</v>
       </c>
-      <c r="ED5" t="s">
+      <c r="EI5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -2823,18 +2888,18 @@
       <c r="AQ6" t="s">
         <v>133</v>
       </c>
-      <c r="BZ6" s="11"/>
-      <c r="EB6" t="s">
+      <c r="CC6" s="11"/>
+      <c r="EG6" t="s">
         <v>139</v>
       </c>
-      <c r="EC6" t="s">
+      <c r="EH6" t="s">
         <v>162</v>
       </c>
-      <c r="ED6" t="s">
+      <c r="EI6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>183</v>
       </c>
@@ -2935,18 +3000,18 @@
       <c r="AQ7" t="s">
         <v>133</v>
       </c>
-      <c r="BZ7" s="11"/>
-      <c r="EB7" t="s">
+      <c r="CC7" s="11"/>
+      <c r="EG7" t="s">
         <v>139</v>
       </c>
-      <c r="EC7" t="s">
+      <c r="EH7" t="s">
         <v>162</v>
       </c>
-      <c r="ED7" t="s">
+      <c r="EI7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>185</v>
       </c>
@@ -3047,18 +3112,18 @@
       <c r="AQ8" t="s">
         <v>133</v>
       </c>
-      <c r="BZ8" s="11"/>
-      <c r="EB8" t="s">
+      <c r="CC8" s="11"/>
+      <c r="EG8" t="s">
         <v>163</v>
       </c>
-      <c r="EC8" t="s">
+      <c r="EH8" t="s">
         <v>162</v>
       </c>
-      <c r="ED8" t="s">
+      <c r="EI8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>186</v>
       </c>
@@ -3159,18 +3224,18 @@
       <c r="AQ9" t="s">
         <v>133</v>
       </c>
-      <c r="BZ9" s="11"/>
-      <c r="EB9" t="s">
+      <c r="CC9" s="11"/>
+      <c r="EG9" t="s">
         <v>139</v>
       </c>
-      <c r="EC9" t="s">
+      <c r="EH9" t="s">
         <v>162</v>
       </c>
-      <c r="ED9" t="s">
+      <c r="EI9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>189</v>
       </c>
@@ -3271,18 +3336,18 @@
       <c r="AQ10" t="s">
         <v>133</v>
       </c>
-      <c r="BZ10" s="11"/>
-      <c r="EB10" t="s">
+      <c r="CC10" s="11"/>
+      <c r="EG10" t="s">
         <v>139</v>
       </c>
-      <c r="EC10" t="s">
+      <c r="EH10" t="s">
         <v>162</v>
       </c>
-      <c r="ED10" t="s">
+      <c r="EI10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>163</v>
       </c>
@@ -3383,18 +3448,18 @@
       <c r="AQ11" t="s">
         <v>133</v>
       </c>
-      <c r="BZ11" s="11"/>
-      <c r="EB11" t="s">
+      <c r="CC11" s="11"/>
+      <c r="EG11" t="s">
         <v>163</v>
       </c>
-      <c r="EC11" t="s">
+      <c r="EH11" t="s">
         <v>162</v>
       </c>
-      <c r="ED11" t="s">
+      <c r="EI11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>192</v>
       </c>
@@ -3522,128 +3587,134 @@
       <c r="AS12">
         <v>54</v>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="11">
+        <v>72</v>
+      </c>
+      <c r="AU12">
         <v>26.86</v>
       </c>
-      <c r="AU12">
+      <c r="AV12">
         <v>23.61</v>
       </c>
-      <c r="AV12">
+      <c r="AW12">
         <v>6.64</v>
       </c>
-      <c r="AW12" t="s">
+      <c r="AX12" t="s">
         <v>199</v>
       </c>
-      <c r="AX12" t="s">
-        <v>133</v>
-      </c>
       <c r="AY12" t="s">
         <v>133</v>
       </c>
       <c r="AZ12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA12" t="s">
         <v>135</v>
       </c>
-      <c r="BA12">
+      <c r="BB12" s="11">
+        <v>72</v>
+      </c>
+      <c r="BC12">
         <v>54</v>
       </c>
-      <c r="BB12">
+      <c r="BD12">
         <v>24.1</v>
       </c>
-      <c r="BC12">
+      <c r="BE12">
         <v>22.65</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
         <v>5.81</v>
       </c>
-      <c r="BE12" t="s">
+      <c r="BG12" t="s">
         <v>199</v>
       </c>
-      <c r="BF12" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX12" t="s">
+      <c r="BH12" t="s">
+        <v>133</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA12" t="s">
         <v>200</v>
       </c>
-      <c r="BY12">
+      <c r="CB12">
         <v>54</v>
       </c>
-      <c r="BZ12" s="11">
+      <c r="CC12" s="11">
         <v>72</v>
       </c>
-      <c r="CA12">
+      <c r="CD12">
         <v>11.58</v>
       </c>
-      <c r="CB12">
+      <c r="CE12">
         <v>9.56</v>
       </c>
-      <c r="CC12">
+      <c r="CF12">
         <v>4.03</v>
       </c>
-      <c r="CD12" t="s">
+      <c r="CG12" t="s">
         <v>199</v>
       </c>
-      <c r="CE12" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>133</v>
-      </c>
-      <c r="CX12">
+      <c r="CH12" t="s">
+        <v>133</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>133</v>
+      </c>
+      <c r="DC12">
         <v>23</v>
       </c>
-      <c r="CY12">
+      <c r="DD12">
         <v>72</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>6</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>72</v>
       </c>
-      <c r="DF12">
+      <c r="DK12">
         <v>4</v>
       </c>
-      <c r="DG12">
+      <c r="DL12">
         <v>72</v>
       </c>
-      <c r="DH12">
+      <c r="DM12">
         <v>4</v>
       </c>
-      <c r="DI12">
+      <c r="DN12">
         <v>72</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>2</v>
       </c>
-      <c r="DQ12">
+      <c r="DV12">
         <v>72</v>
       </c>
-      <c r="DT12">
+      <c r="DY12">
         <v>1</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>72</v>
       </c>
-      <c r="DZ12">
+      <c r="EE12">
         <v>1</v>
       </c>
-      <c r="EA12">
+      <c r="EF12">
         <v>72</v>
       </c>
-      <c r="EB12" t="s">
+      <c r="EG12" t="s">
         <v>163</v>
       </c>
-      <c r="EC12" t="s">
+      <c r="EH12" t="s">
         <v>162</v>
       </c>
-      <c r="ED12" t="s">
+      <c r="EI12" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>201</v>
       </c>
@@ -3771,128 +3842,134 @@
       <c r="AS13">
         <v>49</v>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="11">
+        <v>65</v>
+      </c>
+      <c r="AU13">
         <v>26.2</v>
       </c>
-      <c r="AU13">
+      <c r="AV13">
         <v>23.41</v>
       </c>
-      <c r="AV13">
+      <c r="AW13">
         <v>6.14</v>
       </c>
-      <c r="AW13" t="s">
+      <c r="AX13" t="s">
         <v>199</v>
       </c>
-      <c r="AX13" t="s">
-        <v>133</v>
-      </c>
       <c r="AY13" t="s">
         <v>133</v>
       </c>
       <c r="AZ13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA13" t="s">
         <v>135</v>
       </c>
-      <c r="BA13">
+      <c r="BB13" s="11">
+        <v>65</v>
+      </c>
+      <c r="BC13">
         <v>49</v>
       </c>
-      <c r="BB13">
+      <c r="BD13">
         <v>23.65</v>
       </c>
-      <c r="BC13">
+      <c r="BE13">
         <v>21.82</v>
       </c>
-      <c r="BD13">
+      <c r="BF13">
         <v>5.85</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BG13" t="s">
         <v>199</v>
       </c>
-      <c r="BF13" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX13" t="s">
+      <c r="BH13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA13" t="s">
         <v>200</v>
       </c>
-      <c r="BY13">
+      <c r="CB13">
         <v>49</v>
       </c>
-      <c r="BZ13" s="11">
+      <c r="CC13" s="11">
         <v>65</v>
       </c>
-      <c r="CA13">
+      <c r="CD13">
         <v>12.91</v>
       </c>
-      <c r="CB13">
+      <c r="CE13">
         <v>9.8800000000000008</v>
       </c>
-      <c r="CC13">
+      <c r="CF13">
         <v>4.1500000000000004</v>
       </c>
-      <c r="CD13" t="s">
+      <c r="CG13" t="s">
         <v>199</v>
       </c>
-      <c r="CE13" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF13" t="s">
-        <v>133</v>
-      </c>
-      <c r="CX13">
+      <c r="CH13" t="s">
+        <v>133</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>133</v>
+      </c>
+      <c r="DC13">
         <v>14</v>
       </c>
-      <c r="CY13">
+      <c r="DD13">
         <v>65</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>3</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>65</v>
       </c>
-      <c r="DF13">
+      <c r="DK13">
         <v>4</v>
       </c>
-      <c r="DG13">
+      <c r="DL13">
         <v>65</v>
       </c>
-      <c r="DH13">
+      <c r="DM13">
         <v>0</v>
       </c>
-      <c r="DI13">
+      <c r="DN13">
         <v>65</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>0</v>
       </c>
-      <c r="DQ13">
+      <c r="DV13">
         <v>65</v>
       </c>
-      <c r="DT13">
+      <c r="DY13">
         <v>3</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>65</v>
       </c>
-      <c r="DZ13">
+      <c r="EE13">
         <v>2</v>
       </c>
-      <c r="EA13">
+      <c r="EF13">
         <v>65</v>
       </c>
-      <c r="EB13" t="s">
+      <c r="EG13" t="s">
         <v>139</v>
       </c>
-      <c r="EC13" t="s">
+      <c r="EH13" t="s">
         <v>162</v>
       </c>
-      <c r="ED13" t="s">
+      <c r="EI13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>206</v>
       </c>
@@ -4020,128 +4097,134 @@
       <c r="AS14">
         <v>51</v>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="11">
+        <v>68</v>
+      </c>
+      <c r="AU14">
         <v>27.26</v>
       </c>
-      <c r="AU14">
+      <c r="AV14">
         <v>22.22</v>
       </c>
-      <c r="AV14">
+      <c r="AW14">
         <v>6.5</v>
       </c>
-      <c r="AW14" t="s">
+      <c r="AX14" t="s">
         <v>199</v>
       </c>
-      <c r="AX14" t="s">
-        <v>133</v>
-      </c>
       <c r="AY14" t="s">
         <v>133</v>
       </c>
       <c r="AZ14" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA14" t="s">
         <v>135</v>
       </c>
-      <c r="BA14">
+      <c r="BB14" s="11">
+        <v>68</v>
+      </c>
+      <c r="BC14">
         <v>51</v>
       </c>
-      <c r="BB14">
+      <c r="BD14">
         <v>24.59</v>
       </c>
-      <c r="BC14">
+      <c r="BE14">
         <v>22.53</v>
       </c>
-      <c r="BD14">
+      <c r="BF14">
         <v>5.41</v>
       </c>
-      <c r="BE14" t="s">
+      <c r="BG14" t="s">
         <v>199</v>
       </c>
-      <c r="BF14" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX14" t="s">
+      <c r="BH14" t="s">
+        <v>133</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA14" t="s">
         <v>200</v>
       </c>
-      <c r="BY14">
+      <c r="CB14">
         <v>51</v>
       </c>
-      <c r="BZ14" s="11">
+      <c r="CC14" s="11">
         <v>68</v>
       </c>
-      <c r="CA14">
+      <c r="CD14">
         <v>11.54</v>
       </c>
-      <c r="CB14">
+      <c r="CE14">
         <v>9.06</v>
       </c>
-      <c r="CC14">
+      <c r="CF14">
         <v>4.08</v>
       </c>
-      <c r="CD14" t="s">
+      <c r="CG14" t="s">
         <v>199</v>
       </c>
-      <c r="CE14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>133</v>
-      </c>
-      <c r="CX14">
+      <c r="CH14" t="s">
+        <v>133</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>133</v>
+      </c>
+      <c r="DC14">
         <v>23</v>
       </c>
-      <c r="CY14">
+      <c r="DD14">
         <v>68</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>2</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>68</v>
       </c>
-      <c r="DF14">
+      <c r="DK14">
         <v>5</v>
       </c>
-      <c r="DG14">
+      <c r="DL14">
         <v>68</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>2</v>
       </c>
-      <c r="DI14">
+      <c r="DN14">
         <v>68</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>8</v>
       </c>
-      <c r="DQ14">
+      <c r="DV14">
         <v>68</v>
       </c>
-      <c r="DT14">
+      <c r="DY14">
         <v>5</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>68</v>
       </c>
-      <c r="DZ14">
+      <c r="EE14">
         <v>0</v>
       </c>
-      <c r="EA14">
+      <c r="EF14">
         <v>68</v>
       </c>
-      <c r="EB14" t="s">
+      <c r="EG14" t="s">
         <v>139</v>
       </c>
-      <c r="EC14" t="s">
+      <c r="EH14" t="s">
         <v>162</v>
       </c>
-      <c r="ED14" t="s">
+      <c r="EI14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -4269,128 +4352,134 @@
       <c r="AS15">
         <v>56</v>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="11">
+        <v>71</v>
+      </c>
+      <c r="AU15">
         <v>27.49</v>
       </c>
-      <c r="AU15">
+      <c r="AV15">
         <v>19.52</v>
       </c>
-      <c r="AV15">
+      <c r="AW15">
         <v>5.1100000000000003</v>
       </c>
-      <c r="AW15" t="s">
+      <c r="AX15" t="s">
         <v>199</v>
       </c>
-      <c r="AX15" t="s">
-        <v>133</v>
-      </c>
       <c r="AY15" t="s">
         <v>133</v>
       </c>
       <c r="AZ15" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA15" t="s">
         <v>135</v>
       </c>
-      <c r="BA15">
+      <c r="BB15" s="11">
+        <v>71</v>
+      </c>
+      <c r="BC15">
         <v>56</v>
       </c>
-      <c r="BB15">
+      <c r="BD15">
         <v>23.65</v>
       </c>
-      <c r="BC15">
+      <c r="BE15">
         <v>21.45</v>
       </c>
-      <c r="BD15">
+      <c r="BF15">
         <v>5.13</v>
       </c>
-      <c r="BE15" t="s">
+      <c r="BG15" t="s">
         <v>199</v>
       </c>
-      <c r="BF15" t="s">
-        <v>133</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>133</v>
-      </c>
-      <c r="BX15" t="s">
+      <c r="BH15" t="s">
+        <v>133</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA15" t="s">
         <v>200</v>
       </c>
-      <c r="BY15">
+      <c r="CB15">
         <v>56</v>
       </c>
-      <c r="BZ15" s="11">
+      <c r="CC15" s="11">
         <v>71</v>
       </c>
-      <c r="CA15">
+      <c r="CD15">
         <v>12.58</v>
       </c>
-      <c r="CB15">
+      <c r="CE15">
         <v>8.5</v>
       </c>
-      <c r="CC15">
+      <c r="CF15">
         <v>4.09</v>
       </c>
-      <c r="CD15" t="s">
+      <c r="CG15" t="s">
         <v>199</v>
       </c>
-      <c r="CE15" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF15" t="s">
-        <v>133</v>
-      </c>
-      <c r="CX15">
+      <c r="CH15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CI15" t="s">
+        <v>133</v>
+      </c>
+      <c r="DC15">
         <v>36</v>
       </c>
-      <c r="CY15">
+      <c r="DD15">
         <v>71</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>5</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>71</v>
       </c>
-      <c r="DF15">
+      <c r="DK15">
         <v>6</v>
       </c>
-      <c r="DG15">
+      <c r="DL15">
         <v>71</v>
       </c>
-      <c r="DH15">
+      <c r="DM15">
         <v>6</v>
       </c>
-      <c r="DI15">
+      <c r="DN15">
         <v>71</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>0</v>
       </c>
-      <c r="DQ15">
+      <c r="DV15">
         <v>71</v>
       </c>
-      <c r="DT15">
+      <c r="DY15">
         <v>5</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>71</v>
       </c>
-      <c r="DZ15">
+      <c r="EE15">
         <v>8</v>
       </c>
-      <c r="EA15">
+      <c r="EF15">
         <v>71</v>
       </c>
-      <c r="EB15" t="s">
+      <c r="EG15" t="s">
         <v>213</v>
       </c>
-      <c r="EC15" t="s">
+      <c r="EH15" t="s">
         <v>162</v>
       </c>
-      <c r="ED15" t="s">
+      <c r="EI15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>214</v>
       </c>
@@ -4461,60 +4550,60 @@
         <v>219</v>
       </c>
       <c r="AL16" s="11"/>
-      <c r="BZ16" s="11"/>
-      <c r="CX16">
+      <c r="CC16" s="11"/>
+      <c r="DC16">
         <v>16</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>34</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>0</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>34</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>0</v>
       </c>
-      <c r="DC16">
+      <c r="DH16">
         <v>34</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>2</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>34</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>7</v>
       </c>
-      <c r="DG16">
+      <c r="DL16">
         <v>34</v>
       </c>
-      <c r="DH16">
+      <c r="DM16">
         <v>0</v>
       </c>
-      <c r="DI16">
+      <c r="DN16">
         <v>34</v>
       </c>
-      <c r="DJ16">
+      <c r="DO16">
         <v>5</v>
       </c>
-      <c r="DK16">
+      <c r="DP16">
         <v>34</v>
       </c>
-      <c r="EB16" t="s">
+      <c r="EG16" t="s">
         <v>163</v>
       </c>
-      <c r="EC16" t="s">
+      <c r="EH16" t="s">
         <v>220</v>
       </c>
-      <c r="ED16" t="s">
+      <c r="EI16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>221</v>
       </c>
@@ -4585,60 +4674,60 @@
         <v>223</v>
       </c>
       <c r="AL17" s="11"/>
-      <c r="BZ17" s="11"/>
-      <c r="CX17">
+      <c r="CC17" s="11"/>
+      <c r="DC17">
         <v>34</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>35</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>5</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>35</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>0</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>35</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>10</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>35</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>4</v>
       </c>
-      <c r="DG17">
+      <c r="DL17">
         <v>35</v>
       </c>
-      <c r="DH17">
+      <c r="DM17">
         <v>12</v>
       </c>
-      <c r="DI17">
+      <c r="DN17">
         <v>35</v>
       </c>
-      <c r="DJ17">
+      <c r="DO17">
         <v>21</v>
       </c>
-      <c r="DK17">
+      <c r="DP17">
         <v>35</v>
       </c>
-      <c r="EB17" t="s">
+      <c r="EG17" t="s">
         <v>139</v>
       </c>
-      <c r="EC17" t="s">
+      <c r="EH17" t="s">
         <v>220</v>
       </c>
-      <c r="ED17" t="s">
+      <c r="EI17" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:134" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:139" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>224</v>
       </c>
@@ -4709,60 +4798,60 @@
         <v>228</v>
       </c>
       <c r="AL18" s="11"/>
-      <c r="BZ18" s="11"/>
-      <c r="CX18">
+      <c r="CC18" s="11"/>
+      <c r="DC18">
         <v>15</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>36</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>0</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>36</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>3</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>36</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>1</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>36</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>1</v>
       </c>
-      <c r="DG18">
+      <c r="DL18">
         <v>36</v>
       </c>
-      <c r="DH18">
+      <c r="DM18">
         <v>0</v>
       </c>
-      <c r="DI18">
+      <c r="DN18">
         <v>36</v>
       </c>
-      <c r="DJ18">
+      <c r="DO18">
         <v>5</v>
       </c>
-      <c r="DK18">
+      <c r="DP18">
         <v>36</v>
       </c>
-      <c r="EB18" t="s">
+      <c r="EG18" t="s">
         <v>213</v>
       </c>
-      <c r="EC18" t="s">
+      <c r="EH18" t="s">
         <v>220</v>
       </c>
-      <c r="ED18" t="s">
+      <c r="EI18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>163</v>
       </c>
@@ -4830,48 +4919,48 @@
         <v>233</v>
       </c>
       <c r="AL19" s="11"/>
-      <c r="BZ19" s="11"/>
-      <c r="CX19">
+      <c r="CC19" s="11"/>
+      <c r="DC19">
         <v>2</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>63</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>1</v>
       </c>
-      <c r="DE19">
+      <c r="DJ19">
         <v>63</v>
       </c>
-      <c r="DH19">
+      <c r="DM19">
         <v>1</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>63</v>
       </c>
-      <c r="DJ19" s="8">
+      <c r="DO19" s="8">
         <v>0</v>
       </c>
-      <c r="DK19">
+      <c r="DP19">
         <v>63</v>
       </c>
-      <c r="DN19">
+      <c r="DS19">
         <v>1</v>
       </c>
-      <c r="DO19">
+      <c r="DT19">
         <v>59</v>
       </c>
-      <c r="EB19" t="s">
+      <c r="EG19" t="s">
         <v>163</v>
       </c>
-      <c r="EC19" t="s">
+      <c r="EH19" t="s">
         <v>220</v>
       </c>
-      <c r="ED19" t="s">
+      <c r="EI19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>234</v>
       </c>
@@ -4945,48 +5034,48 @@
         <v>233</v>
       </c>
       <c r="AL20" s="11"/>
-      <c r="BZ20" s="11"/>
-      <c r="CX20">
+      <c r="CC20" s="11"/>
+      <c r="DC20">
         <v>32</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>63</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>7</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>63</v>
       </c>
-      <c r="DH20">
+      <c r="DM20">
         <v>16</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>63</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>16</v>
       </c>
-      <c r="DK20">
+      <c r="DP20">
         <v>63</v>
       </c>
-      <c r="DN20">
+      <c r="DS20">
         <v>5</v>
       </c>
-      <c r="DO20">
+      <c r="DT20">
         <v>62</v>
       </c>
-      <c r="EB20" t="s">
+      <c r="EG20" t="s">
         <v>139</v>
       </c>
-      <c r="EC20" t="s">
+      <c r="EH20" t="s">
         <v>220</v>
       </c>
-      <c r="ED20" t="s">
+      <c r="EI20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>235</v>
       </c>
@@ -5057,48 +5146,48 @@
         <v>141</v>
       </c>
       <c r="AL21" s="11"/>
-      <c r="BZ21" s="11"/>
-      <c r="CX21">
+      <c r="CC21" s="11"/>
+      <c r="DC21">
         <v>1</v>
       </c>
-      <c r="CY21">
+      <c r="DD21">
         <v>12</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>1</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>12</v>
       </c>
-      <c r="DJ21">
+      <c r="DO21">
         <v>0</v>
       </c>
-      <c r="DK21">
+      <c r="DP21">
         <v>12</v>
       </c>
-      <c r="DL21">
+      <c r="DQ21">
         <v>0</v>
       </c>
-      <c r="DM21">
+      <c r="DR21">
         <v>12</v>
       </c>
-      <c r="DN21">
+      <c r="DS21">
         <v>0</v>
       </c>
-      <c r="DO21">
+      <c r="DT21">
         <v>12</v>
       </c>
-      <c r="EB21" t="s">
+      <c r="EG21" t="s">
         <v>139</v>
       </c>
-      <c r="EC21" t="s">
+      <c r="EH21" t="s">
         <v>220</v>
       </c>
-      <c r="ED21" t="s">
+      <c r="EI21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>238</v>
       </c>
@@ -5169,48 +5258,48 @@
         <v>141</v>
       </c>
       <c r="AL22" s="11"/>
-      <c r="BZ22" s="11"/>
-      <c r="CX22">
+      <c r="CC22" s="11"/>
+      <c r="DC22">
         <v>1</v>
       </c>
-      <c r="CY22">
+      <c r="DD22">
         <v>12</v>
       </c>
-      <c r="DH22">
+      <c r="DM22">
         <v>0</v>
       </c>
-      <c r="DI22">
+      <c r="DN22">
         <v>12</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>1</v>
       </c>
-      <c r="DK22">
+      <c r="DP22">
         <v>12</v>
       </c>
-      <c r="DL22">
+      <c r="DQ22">
         <v>0</v>
       </c>
-      <c r="DM22">
+      <c r="DR22">
         <v>12</v>
       </c>
-      <c r="DN22">
+      <c r="DS22">
         <v>0</v>
       </c>
-      <c r="DO22">
+      <c r="DT22">
         <v>12</v>
       </c>
-      <c r="EB22" t="s">
+      <c r="EG22" t="s">
         <v>139</v>
       </c>
-      <c r="EC22" t="s">
+      <c r="EH22" t="s">
         <v>220</v>
       </c>
-      <c r="ED22" t="s">
+      <c r="EI22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>163</v>
       </c>
@@ -5281,48 +5370,48 @@
         <v>191</v>
       </c>
       <c r="AL23" s="11"/>
-      <c r="BZ23" s="11"/>
-      <c r="CX23">
+      <c r="CC23" s="11"/>
+      <c r="DC23">
         <v>1</v>
       </c>
-      <c r="CY23">
+      <c r="DD23">
         <v>24</v>
       </c>
-      <c r="DH23">
+      <c r="DM23">
         <v>0</v>
       </c>
-      <c r="DI23">
+      <c r="DN23">
         <v>24</v>
       </c>
-      <c r="DJ23">
+      <c r="DO23">
         <v>0</v>
       </c>
-      <c r="DK23">
+      <c r="DP23">
         <v>24</v>
       </c>
-      <c r="DL23">
+      <c r="DQ23">
         <v>0</v>
       </c>
-      <c r="DM23">
+      <c r="DR23">
         <v>24</v>
       </c>
-      <c r="DN23">
+      <c r="DS23">
         <v>0</v>
       </c>
-      <c r="DO23">
+      <c r="DT23">
         <v>24</v>
       </c>
-      <c r="EB23" t="s">
+      <c r="EG23" t="s">
         <v>163</v>
       </c>
-      <c r="EC23" t="s">
+      <c r="EH23" t="s">
         <v>220</v>
       </c>
-      <c r="ED23" t="s">
+      <c r="EI23" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>238</v>
       </c>
@@ -5381,24 +5470,24 @@
         <v>152</v>
       </c>
       <c r="AL24" s="11"/>
-      <c r="BZ24" s="11"/>
-      <c r="CX24" s="6">
+      <c r="CC24" s="11"/>
+      <c r="DC24" s="6">
         <v>6</v>
       </c>
-      <c r="CY24" s="6">
+      <c r="DD24" s="6">
         <v>15</v>
       </c>
-      <c r="EB24" t="s">
+      <c r="EG24" t="s">
         <v>139</v>
       </c>
-      <c r="EC24" t="s">
+      <c r="EH24" t="s">
         <v>220</v>
       </c>
-      <c r="ED24" t="s">
+      <c r="EI24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>242</v>
       </c>
@@ -5457,24 +5546,24 @@
         <v>152</v>
       </c>
       <c r="AL25" s="11"/>
-      <c r="BZ25" s="11"/>
-      <c r="CX25" s="6">
+      <c r="CC25" s="11"/>
+      <c r="DC25" s="6">
         <v>1</v>
       </c>
-      <c r="CY25" s="6">
+      <c r="DD25" s="6">
         <v>13</v>
       </c>
-      <c r="EB25" t="s">
+      <c r="EG25" t="s">
         <v>139</v>
       </c>
-      <c r="EC25" t="s">
+      <c r="EH25" t="s">
         <v>220</v>
       </c>
-      <c r="ED25" t="s">
+      <c r="EI25" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:134" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:139" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>163</v>
       </c>
@@ -5533,20 +5622,20 @@
         <v>152</v>
       </c>
       <c r="AL26" s="11"/>
-      <c r="BZ26" s="11"/>
-      <c r="CX26" s="6">
+      <c r="CC26" s="11"/>
+      <c r="DC26" s="6">
         <v>2</v>
       </c>
-      <c r="CY26" s="6">
+      <c r="DD26" s="6">
         <v>14</v>
       </c>
-      <c r="EB26" t="s">
+      <c r="EG26" t="s">
         <v>163</v>
       </c>
-      <c r="EC26" t="s">
+      <c r="EH26" t="s">
         <v>220</v>
       </c>
-      <c r="ED26" t="s">
+      <c r="EI26" t="s">
         <v>133</v>
       </c>
     </row>
